--- a/Digitised_Records_2026_03_13.xlsx
+++ b/Digitised_Records_2026_03_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63C838ED-CCB0-4BF9-9BBD-3A8E0AE0578A}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A97D1FD4-5BEF-4D9D-8C5C-A33E8CD1BA8A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
@@ -12768,7 +12768,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>396</v>
       </c>
@@ -19870,10 +19870,10 @@
         <v>74</v>
       </c>
       <c r="D369" s="5">
-        <v>-37</v>
+        <v>-37.860917999999998</v>
       </c>
       <c r="E369" s="5">
-        <v>144.91</v>
+        <v>144.90595300000001</v>
       </c>
       <c r="F369" s="3">
         <v>1927</v>
@@ -19915,7 +19915,7 @@
         <v>74</v>
       </c>
       <c r="D370" s="5">
-        <v>-37</v>
+        <v>-37.860917999999998</v>
       </c>
       <c r="E370" s="5">
         <v>144.91</v>

--- a/Digitised_Records_2026_03_13.xlsx
+++ b/Digitised_Records_2026_03_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sotonac-my.sharepoint.com/personal/ck1g20_soton_ac_uk/Documents/Documents/PhD/20_Historical_record_catalogue/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C18AE1-0225-4E0F-9A9D-4714FDC840B0}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{22737A28-F927-43B1-8C9E-30BC7D7DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2FB24D4-A7D6-4752-B26F-EFAF76785A66}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FB86131-9B33-41BE-BB40-45738662AB11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3751" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="757">
   <si>
     <t>Study</t>
   </si>
@@ -2391,6 +2391,9 @@
   </si>
   <si>
     <t>1980, 1983 - 1987, 1991 - 1994, 1996 - 1998, 2002, 2009 - 2011</t>
+  </si>
+  <si>
+    <t>January 1925</t>
   </si>
 </sst>
 </file>
@@ -2663,7 +2666,6 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2714,6 +2716,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3460,8 +3463,8 @@
         <f t="shared" si="0"/>
         <v>67.900000000000006</v>
       </c>
-      <c r="I9" s="10">
-        <v>9133</v>
+      <c r="I9" s="46" t="s">
+        <v>756</v>
       </c>
       <c r="J9" s="5">
         <v>0.1</v>
@@ -3912,7 +3915,7 @@
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J19" s="5">
@@ -3959,7 +3962,7 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="10" t="s">
         <v>57</v>
       </c>
       <c r="J20" s="5">
@@ -4005,7 +4008,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J21" s="5">
@@ -4089,14 +4092,14 @@
       <c r="F23" s="3">
         <v>1841</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="11">
         <v>2002</v>
       </c>
       <c r="H23" s="5">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="J23" s="5">
@@ -4135,14 +4138,14 @@
       <c r="F24" s="3">
         <v>1951</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>1994</v>
       </c>
       <c r="H24" s="5">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J24" s="5">
@@ -4180,14 +4183,14 @@
       <c r="F25" s="3">
         <v>1951</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>1979</v>
       </c>
       <c r="H25" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J25" s="5">
@@ -4225,14 +4228,14 @@
       <c r="F26" s="3">
         <v>1951</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>1979</v>
       </c>
       <c r="H26" s="5">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J26" s="5">
@@ -4270,14 +4273,14 @@
       <c r="F27" s="3">
         <v>1963</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="11">
         <v>1991</v>
       </c>
       <c r="H27" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="10" t="s">
         <v>76</v>
       </c>
       <c r="J27" s="5">
@@ -4316,14 +4319,14 @@
       <c r="F28" s="3">
         <v>1983</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>1998</v>
       </c>
       <c r="H28" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J28" s="5">
@@ -4361,14 +4364,14 @@
       <c r="F29" s="3">
         <v>1929</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>1936</v>
       </c>
       <c r="H29" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J29" s="5">
@@ -4406,14 +4409,14 @@
       <c r="F30" s="3">
         <v>1942</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>1943</v>
       </c>
       <c r="H30" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J30" s="5">
@@ -4451,14 +4454,14 @@
       <c r="F31" s="3">
         <v>1942</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="11">
         <v>1943</v>
       </c>
       <c r="H31" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J31" s="5">
@@ -4496,14 +4499,14 @@
       <c r="F32" s="3">
         <v>1943</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="11">
         <v>1944</v>
       </c>
       <c r="H32" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J32" s="5">
@@ -4541,14 +4544,14 @@
       <c r="F33" s="3">
         <v>1943</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>1944</v>
       </c>
       <c r="H33" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J33" s="5">
@@ -4586,14 +4589,14 @@
       <c r="F34" s="3">
         <v>1943</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>1944</v>
       </c>
       <c r="H34" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J34" s="5">
@@ -4631,14 +4634,14 @@
       <c r="F35" s="3">
         <v>1993</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="11">
         <v>1998</v>
       </c>
       <c r="H35" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J35" s="5">
@@ -4676,14 +4679,14 @@
       <c r="F36" s="3">
         <v>1955</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>1968</v>
       </c>
       <c r="H36" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J36" s="5">
@@ -4721,14 +4724,14 @@
       <c r="F37" s="3">
         <v>1955</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>1968</v>
       </c>
       <c r="H37" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J37" s="5">
@@ -4766,14 +4769,14 @@
       <c r="F38" s="3">
         <v>1955</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>1967</v>
       </c>
       <c r="H38" s="5">
         <f>(1+(G38-F38))-J38</f>
         <v>13</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J38" s="5">
@@ -4811,14 +4814,14 @@
       <c r="F39" s="3">
         <v>1955</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="11">
         <v>1964</v>
       </c>
       <c r="H39" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J39" s="5">
@@ -4856,14 +4859,14 @@
       <c r="F40" s="3">
         <v>1956</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="11">
         <v>1961</v>
       </c>
       <c r="H40" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J40" s="5">
@@ -4901,14 +4904,14 @@
       <c r="F41" s="3">
         <v>1955</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="11">
         <v>1968</v>
       </c>
       <c r="H41" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J41" s="5">
@@ -4946,14 +4949,14 @@
       <c r="F42" s="3">
         <v>1948</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>1968</v>
       </c>
       <c r="H42" s="5">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J42" s="5">
@@ -4991,14 +4994,14 @@
       <c r="F43" s="3">
         <v>1955</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>1968</v>
       </c>
       <c r="H43" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J43" s="5">
@@ -5036,14 +5039,14 @@
       <c r="F44" s="3">
         <v>1965</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>1968</v>
       </c>
       <c r="H44" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J44" s="5">
@@ -5081,14 +5084,14 @@
       <c r="F45" s="3">
         <v>1937</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="11">
         <v>1948</v>
       </c>
       <c r="H45" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J45" s="5">
@@ -5126,14 +5129,14 @@
       <c r="F46" s="3">
         <v>1921</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="11">
         <v>1923</v>
       </c>
       <c r="H46" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J46" s="5">
@@ -5171,14 +5174,14 @@
       <c r="F47" s="3">
         <v>1933</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>1949</v>
       </c>
       <c r="H47" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J47" s="5">
@@ -5216,14 +5219,14 @@
       <c r="F48" s="3">
         <v>1968</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>1970</v>
       </c>
       <c r="H48" s="5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J48" s="5">
@@ -5261,14 +5264,14 @@
       <c r="F49" s="3">
         <v>1947</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="11">
         <v>1950</v>
       </c>
       <c r="H49" s="5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J49" s="5">
@@ -5306,14 +5309,14 @@
       <c r="F50" s="3">
         <v>1954</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="11">
         <v>1966</v>
       </c>
       <c r="H50" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J50" s="5">
@@ -5351,14 +5354,14 @@
       <c r="F51" s="3">
         <v>1967</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="11">
         <v>1967</v>
       </c>
       <c r="H51" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J51" s="5">
@@ -5396,14 +5399,14 @@
       <c r="F52" s="3">
         <v>1907</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="11">
         <v>1974</v>
       </c>
       <c r="H52" s="5">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J52" s="5">
@@ -5441,14 +5444,14 @@
       <c r="F53" s="3">
         <v>1987</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G53" s="11">
         <v>1996</v>
       </c>
       <c r="H53" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J53" s="5">
@@ -5486,14 +5489,14 @@
       <c r="F54" s="3">
         <v>1984</v>
       </c>
-      <c r="G54" s="12">
+      <c r="G54" s="11">
         <v>1992</v>
       </c>
       <c r="H54" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J54" s="5">
@@ -5531,14 +5534,14 @@
       <c r="F55" s="3">
         <v>1854</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="11">
         <v>1877</v>
       </c>
       <c r="H55" s="5">
         <f t="shared" si="0"/>
         <v>23.5</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="10" t="s">
         <v>118</v>
       </c>
       <c r="J55" s="5">
@@ -5576,14 +5579,14 @@
       <c r="F56" s="3">
         <v>1897</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G56" s="11">
         <v>2000</v>
       </c>
       <c r="H56" s="5">
         <f t="shared" si="0"/>
         <v>103.5</v>
       </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="10" t="s">
         <v>697</v>
       </c>
       <c r="J56" s="5">
@@ -5719,7 +5722,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="10" t="s">
         <v>129</v>
       </c>
       <c r="J59" s="5">
@@ -5764,7 +5767,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="10" t="s">
         <v>132</v>
       </c>
       <c r="J60" s="5">
@@ -5810,7 +5813,7 @@
         <f>(1+(G61-F61))-J61</f>
         <v>119</v>
       </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="10" t="s">
         <v>134</v>
       </c>
       <c r="J61" s="5">
@@ -6056,14 +6059,14 @@
         <v>143</v>
       </c>
     </row>
-    <row r="67" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="13" t="s">
+    <row r="67" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D67" s="8">
@@ -6072,51 +6075,51 @@
       <c r="E67" s="8">
         <v>12.337565</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="11">
         <v>1872</v>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="11">
         <v>1897</v>
       </c>
       <c r="H67" s="5">
         <f t="shared" si="0"/>
         <v>24.76</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="I67" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="J67" s="15">
+      <c r="J67" s="14">
         <v>1.24</v>
       </c>
-      <c r="K67" s="12" t="s">
+      <c r="K67" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L67" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M67" s="12" t="s">
+      <c r="L67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M67" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N67" s="16" t="s">
+      <c r="N67" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O67" s="17"/>
-      <c r="P67" s="17"/>
-      <c r="Q67" s="17"/>
-      <c r="R67" s="17"/>
-      <c r="S67" s="17"/>
-      <c r="T67" s="17"/>
-      <c r="U67" s="17"/>
-      <c r="V67" s="17"/>
-    </row>
-    <row r="68" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="13" t="s">
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16"/>
+      <c r="S67" s="16"/>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16"/>
+      <c r="V67" s="16"/>
+    </row>
+    <row r="68" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D68" s="8">
@@ -6125,51 +6128,51 @@
       <c r="E68" s="8">
         <v>12.330005999999999</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="11">
         <v>1897</v>
       </c>
-      <c r="G68" s="12">
+      <c r="G68" s="11">
         <v>1908</v>
       </c>
       <c r="H68" s="5">
         <f t="shared" si="0"/>
         <v>2.59</v>
       </c>
-      <c r="I68" s="12" t="s">
+      <c r="I68" s="11" t="s">
         <v>151</v>
       </c>
       <c r="J68">
         <v>9.41</v>
       </c>
-      <c r="K68" s="12" t="s">
+      <c r="K68" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L68" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M68" s="12" t="s">
+      <c r="L68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M68" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N68" s="16" t="s">
+      <c r="N68" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O68" s="17"/>
-      <c r="P68" s="17"/>
-      <c r="Q68" s="17"/>
-      <c r="R68" s="17"/>
-      <c r="S68" s="17"/>
-      <c r="T68" s="17"/>
-      <c r="U68" s="17"/>
-      <c r="V68" s="17"/>
-    </row>
-    <row r="69" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="13" t="s">
+      <c r="O68" s="16"/>
+      <c r="P68" s="16"/>
+      <c r="Q68" s="16"/>
+      <c r="R68" s="16"/>
+      <c r="S68" s="16"/>
+      <c r="T68" s="16"/>
+      <c r="U68" s="16"/>
+      <c r="V68" s="16"/>
+    </row>
+    <row r="69" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D69" s="8">
@@ -6178,51 +6181,51 @@
       <c r="E69" s="8">
         <v>12.33</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="11">
         <v>1909</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="11">
         <v>2004</v>
       </c>
       <c r="H69" s="5">
         <f t="shared" si="0"/>
         <v>92.5</v>
       </c>
-      <c r="I69" s="12" t="s">
+      <c r="I69" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="J69" s="15">
+      <c r="J69" s="14">
         <v>3.5</v>
       </c>
-      <c r="K69" s="12" t="s">
+      <c r="K69" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L69" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M69" s="12" t="s">
+      <c r="L69" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N69" s="16" t="s">
+      <c r="N69" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O69" s="17"/>
-      <c r="P69" s="17"/>
-      <c r="Q69" s="17"/>
-      <c r="R69" s="17"/>
-      <c r="S69" s="17"/>
-      <c r="T69" s="17"/>
-      <c r="U69" s="17"/>
-      <c r="V69" s="17"/>
-    </row>
-    <row r="70" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="13" t="s">
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+    </row>
+    <row r="70" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D70" s="8">
@@ -6231,51 +6234,51 @@
       <c r="E70" s="8">
         <v>12.350166</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="11">
         <v>1910</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="11">
         <v>1910</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="0"/>
         <v>0.17000000000000004</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="I70" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="J70" s="15">
+      <c r="J70" s="14">
         <v>0.83</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="K70" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L70" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M70" s="12" t="s">
+      <c r="L70" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M70" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N70" s="16" t="s">
+      <c r="N70" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O70" s="17"/>
-      <c r="P70" s="17"/>
-      <c r="Q70" s="17"/>
-      <c r="R70" s="17"/>
-      <c r="S70" s="17"/>
-      <c r="T70" s="17"/>
-      <c r="U70" s="17"/>
-      <c r="V70" s="17"/>
-    </row>
-    <row r="71" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="13" t="s">
+      <c r="O70" s="16"/>
+      <c r="P70" s="16"/>
+      <c r="Q70" s="16"/>
+      <c r="R70" s="16"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="16"/>
+      <c r="U70" s="16"/>
+      <c r="V70" s="16"/>
+    </row>
+    <row r="71" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D71" s="8">
@@ -6284,51 +6287,51 @@
       <c r="E71" s="8">
         <v>12.42</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="11">
         <v>1914</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="11">
         <v>1921</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="0"/>
         <v>3.9400000000000004</v>
       </c>
-      <c r="I71" s="12" t="s">
+      <c r="I71" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="J71" s="15">
+      <c r="J71" s="14">
         <v>4.0599999999999996</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L71" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M71" s="12" t="s">
+      <c r="L71" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M71" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N71" s="16" t="s">
+      <c r="N71" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-    </row>
-    <row r="72" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+      <c r="O71" s="16"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+      <c r="T71" s="16"/>
+      <c r="U71" s="16"/>
+      <c r="V71" s="16"/>
+    </row>
+    <row r="72" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D72" s="8">
@@ -6337,51 +6340,51 @@
       <c r="E72" s="8">
         <v>12.332060999999999</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="11">
         <v>1916</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="11">
         <v>1916</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="0"/>
         <v>0.42000000000000004</v>
       </c>
-      <c r="I72" s="12" t="s">
+      <c r="I72" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="J72" s="15">
+      <c r="J72" s="14">
         <v>0.57999999999999996</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L72" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M72" s="12" t="s">
+      <c r="L72" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M72" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N72" s="16" t="s">
+      <c r="N72" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O72" s="17"/>
-      <c r="P72" s="17"/>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17"/>
-      <c r="S72" s="17"/>
-      <c r="T72" s="17"/>
-      <c r="U72" s="17"/>
-      <c r="V72" s="17"/>
-    </row>
-    <row r="73" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="13" t="s">
+      <c r="O72" s="16"/>
+      <c r="P72" s="16"/>
+      <c r="Q72" s="16"/>
+      <c r="R72" s="16"/>
+      <c r="S72" s="16"/>
+      <c r="T72" s="16"/>
+      <c r="U72" s="16"/>
+      <c r="V72" s="16"/>
+    </row>
+    <row r="73" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D73" s="8">
@@ -6390,51 +6393,51 @@
       <c r="E73" s="8">
         <v>12.337096000000001</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="11">
         <v>1919</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="11">
         <v>1919</v>
       </c>
       <c r="H73" s="5">
         <f t="shared" si="0"/>
         <v>7.999999999999996E-2</v>
       </c>
-      <c r="I73" s="12" t="s">
+      <c r="I73" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="J73" s="15">
+      <c r="J73" s="14">
         <v>0.92</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L73" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M73" s="12" t="s">
+      <c r="L73" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M73" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N73" s="16" t="s">
+      <c r="N73" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="O73" s="17"/>
-      <c r="P73" s="17"/>
-      <c r="Q73" s="17"/>
-      <c r="R73" s="17"/>
-      <c r="S73" s="17"/>
-      <c r="T73" s="17"/>
-      <c r="U73" s="17"/>
-      <c r="V73" s="17"/>
+      <c r="O73" s="16"/>
+      <c r="P73" s="16"/>
+      <c r="Q73" s="16"/>
+      <c r="R73" s="16"/>
+      <c r="S73" s="16"/>
+      <c r="T73" s="16"/>
+      <c r="U73" s="16"/>
+      <c r="V73" s="16"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D74" s="8">
@@ -6473,13 +6476,13 @@
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D75" s="8">
@@ -6509,7 +6512,7 @@
       <c r="L75" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M75" s="12" t="s">
+      <c r="M75" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="7" t="s">
@@ -6517,13 +6520,13 @@
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D76" s="8">
@@ -6553,7 +6556,7 @@
       <c r="L76" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M76" s="12" t="s">
+      <c r="M76" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="7" t="s">
@@ -6561,13 +6564,13 @@
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D77" s="8">
@@ -6597,7 +6600,7 @@
       <c r="L77" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M77" s="12" t="s">
+      <c r="M77" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="7" t="s">
@@ -6605,13 +6608,13 @@
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="13" t="s">
         <v>147</v>
       </c>
       <c r="D78" s="8">
@@ -6641,7 +6644,7 @@
       <c r="L78" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M78" s="12" t="s">
+      <c r="M78" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="7" t="s">
@@ -6649,13 +6652,13 @@
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D79" s="8">
@@ -6685,7 +6688,7 @@
       <c r="L79" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M79" s="12" t="s">
+      <c r="M79" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="7" t="s">
@@ -6693,13 +6696,13 @@
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D80" s="8">
@@ -6729,7 +6732,7 @@
       <c r="L80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M80" s="12" t="s">
+      <c r="M80" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="7" t="s">
@@ -6737,13 +6740,13 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D81" s="8">
@@ -6773,7 +6776,7 @@
       <c r="L81" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M81" s="12" t="s">
+      <c r="M81" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="7" t="s">
@@ -6781,13 +6784,13 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A82" s="18" t="s">
+      <c r="A82" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D82" s="5">
@@ -6818,7 +6821,7 @@
       <c r="L82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M82" s="12" t="s">
+      <c r="M82" s="11" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
@@ -6826,13 +6829,13 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A83" s="18" t="s">
+      <c r="A83" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D83" s="5">
@@ -6863,18 +6866,18 @@
       <c r="L83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M83" s="12" t="s">
+      <c r="M83" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A84" s="18" t="s">
+      <c r="A84" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D84" s="5">
@@ -6905,18 +6908,18 @@
       <c r="L84" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M84" s="12" t="s">
+      <c r="M84" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D85" s="5">
@@ -6948,18 +6951,18 @@
       <c r="L85" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M85" s="12" t="s">
+      <c r="M85" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A86" s="18" t="s">
+      <c r="A86" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="10" t="s">
         <v>48</v>
       </c>
       <c r="D86" s="5">
@@ -6990,7 +6993,7 @@
       <c r="L86" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M86" s="12" t="s">
+      <c r="M86" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7020,7 +7023,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J87" s="5">
@@ -7065,7 +7068,7 @@
         <f t="shared" si="0"/>
         <v>0.60301163586584527</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="10" t="s">
         <v>188</v>
       </c>
       <c r="J88" s="5">
@@ -7111,7 +7114,7 @@
         <f t="shared" si="0"/>
         <v>1.375</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="10" t="s">
         <v>192</v>
       </c>
       <c r="J89" s="5">
@@ -7202,7 +7205,7 @@
         <f t="shared" si="0"/>
         <v>8.0082135523613984E-2</v>
       </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="10" t="s">
         <v>201</v>
       </c>
       <c r="J91" s="5">
@@ -7248,7 +7251,7 @@
         <f>(1+(G92-F92))-J92</f>
         <v>2.739726027397249E-3</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="10" t="s">
         <v>205</v>
       </c>
       <c r="J92" s="5">
@@ -7294,7 +7297,7 @@
         <f>(1+(G93-F93))-J93</f>
         <v>2.739726027397249E-3</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="10" t="s">
         <v>205</v>
       </c>
       <c r="J93" s="5">
@@ -7450,13 +7453,13 @@
       </c>
     </row>
     <row r="97" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="19" t="s">
+      <c r="A97" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B97" s="20" t="s">
+      <c r="B97" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="C97" s="20" t="s">
+      <c r="C97" s="19" t="s">
         <v>216</v>
       </c>
       <c r="D97" s="5">
@@ -7475,7 +7478,7 @@
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="I97" s="11" t="s">
+      <c r="I97" s="10" t="s">
         <v>217</v>
       </c>
       <c r="J97" s="5">
@@ -7490,18 +7493,18 @@
       <c r="M97" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N97" s="21" t="s">
+      <c r="N97" s="20" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="19" t="s">
+      <c r="A98" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B98" s="20" t="s">
+      <c r="B98" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="C98" s="20" t="s">
+      <c r="C98" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D98" s="5">
@@ -7520,7 +7523,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="I98" s="11" t="s">
+      <c r="I98" s="10" t="s">
         <v>699</v>
       </c>
       <c r="J98" s="5">
@@ -7540,13 +7543,13 @@
       </c>
     </row>
     <row r="99" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="19" t="s">
+      <c r="A99" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C99" s="20" t="s">
+      <c r="C99" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D99" s="5">
@@ -7565,7 +7568,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="I99" s="11" t="s">
+      <c r="I99" s="10" t="s">
         <v>698</v>
       </c>
       <c r="J99" s="5">
@@ -7586,13 +7589,13 @@
       </c>
     </row>
     <row r="100" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="19" t="s">
+      <c r="A100" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B100" s="20" t="s">
+      <c r="B100" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="C100" s="20" t="s">
+      <c r="C100" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="5">
@@ -7611,7 +7614,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I100" s="10" t="s">
         <v>225</v>
       </c>
       <c r="J100" s="5">
@@ -7632,13 +7635,13 @@
       </c>
     </row>
     <row r="101" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="19" t="s">
+      <c r="A101" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B101" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="C101" s="20" t="s">
+      <c r="C101" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D101" s="5">
@@ -7677,13 +7680,13 @@
       </c>
     </row>
     <row r="102" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="19" t="s">
+      <c r="A102" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="C102" s="20" t="s">
+      <c r="C102" s="19" t="s">
         <v>88</v>
       </c>
       <c r="D102" s="5">
@@ -7722,13 +7725,13 @@
       </c>
     </row>
     <row r="103" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="19" t="s">
+      <c r="A103" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B103" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="C103" s="20" t="s">
+      <c r="C103" s="19" t="s">
         <v>230</v>
       </c>
       <c r="D103" s="5">
@@ -7767,13 +7770,13 @@
       </c>
     </row>
     <row r="104" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="19" t="s">
+      <c r="A104" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="C104" s="20" t="s">
+      <c r="C104" s="19" t="s">
         <v>230</v>
       </c>
       <c r="D104" s="5">
@@ -7812,13 +7815,13 @@
       </c>
     </row>
     <row r="105" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="19" t="s">
+      <c r="A105" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="C105" s="20" t="s">
+      <c r="C105" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D105" s="5">
@@ -7857,13 +7860,13 @@
       </c>
     </row>
     <row r="106" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="19" t="s">
+      <c r="A106" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="C106" s="20" t="s">
+      <c r="C106" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D106" s="5">
@@ -7902,13 +7905,13 @@
       </c>
     </row>
     <row r="107" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="19" t="s">
+      <c r="A107" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="C107" s="20" t="s">
+      <c r="C107" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D107" s="5">
@@ -7947,13 +7950,13 @@
       </c>
     </row>
     <row r="108" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="19" t="s">
+      <c r="A108" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D108" s="5">
@@ -7992,13 +7995,13 @@
       </c>
     </row>
     <row r="109" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="20" t="s">
+      <c r="C109" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D109" s="5">
@@ -8017,7 +8020,7 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="I109" s="11" t="s">
+      <c r="I109" s="10" t="s">
         <v>700</v>
       </c>
       <c r="J109" s="5">
@@ -8037,13 +8040,13 @@
       </c>
     </row>
     <row r="110" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="19" t="s">
+      <c r="A110" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="C110" s="20" t="s">
+      <c r="C110" s="19" t="s">
         <v>123</v>
       </c>
       <c r="D110" s="5">
@@ -8062,7 +8065,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="I110" s="11" t="s">
+      <c r="I110" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J110" s="5">
@@ -8082,13 +8085,13 @@
       </c>
     </row>
     <row r="111" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="19" t="s">
+      <c r="A111" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="C111" s="20" t="s">
+      <c r="C111" s="19" t="s">
         <v>123</v>
       </c>
       <c r="D111" s="5">
@@ -8107,7 +8110,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="I111" s="11" t="s">
+      <c r="I111" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J111" s="5">
@@ -8127,13 +8130,13 @@
       </c>
     </row>
     <row r="112" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="19" t="s">
+      <c r="A112" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="19" t="s">
         <v>242</v>
       </c>
       <c r="D112" s="8">
@@ -8152,7 +8155,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="I112" s="11" t="s">
+      <c r="I112" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J112" s="5">
@@ -8172,13 +8175,13 @@
       </c>
     </row>
     <row r="113" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="19" t="s">
+      <c r="A113" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="C113" s="20" t="s">
+      <c r="C113" s="19" t="s">
         <v>242</v>
       </c>
       <c r="D113" s="5">
@@ -8197,7 +8200,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="I113" s="11" t="s">
+      <c r="I113" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J113" s="5">
@@ -8217,13 +8220,13 @@
       </c>
     </row>
     <row r="114" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B114" s="20" t="s">
+      <c r="B114" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="C114" s="20" t="s">
+      <c r="C114" s="19" t="s">
         <v>242</v>
       </c>
       <c r="D114" s="5">
@@ -8242,7 +8245,7 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="I114" s="11" t="s">
+      <c r="I114" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J114" s="5">
@@ -8262,13 +8265,13 @@
       </c>
     </row>
     <row r="115" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="19" t="s">
+      <c r="A115" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B115" s="20" t="s">
+      <c r="B115" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C115" s="20" t="s">
+      <c r="C115" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D115" s="5">
@@ -8287,7 +8290,7 @@
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="I115" s="11" t="s">
+      <c r="I115" s="10" t="s">
         <v>701</v>
       </c>
       <c r="J115" s="5">
@@ -8307,13 +8310,13 @@
       </c>
     </row>
     <row r="116" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="19" t="s">
+      <c r="A116" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="C116" s="20" t="s">
+      <c r="C116" s="19" t="s">
         <v>78</v>
       </c>
       <c r="D116" s="5">
@@ -8332,7 +8335,7 @@
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="I116" s="11" t="s">
+      <c r="I116" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J116" s="5">
@@ -8377,7 +8380,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="I117" s="11" t="s">
+      <c r="I117" s="10" t="s">
         <v>702</v>
       </c>
       <c r="J117" s="5">
@@ -8422,7 +8425,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I118" s="11" t="s">
+      <c r="I118" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J118" s="5">
@@ -8512,7 +8515,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="I120" s="11" t="s">
+      <c r="I120" s="10" t="s">
         <v>703</v>
       </c>
       <c r="J120" s="5">
@@ -8708,7 +8711,7 @@
       <c r="M124" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N124" s="21" t="s">
+      <c r="N124" s="20" t="s">
         <v>259</v>
       </c>
     </row>
@@ -8716,7 +8719,7 @@
       <c r="A125" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B125" s="22" t="s">
+      <c r="B125" s="21" t="s">
         <v>260</v>
       </c>
       <c r="C125" s="3" t="s">
@@ -8753,7 +8756,7 @@
       <c r="M125" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N125" s="21" t="s">
+      <c r="N125" s="20" t="s">
         <v>259</v>
       </c>
     </row>
@@ -8761,7 +8764,7 @@
       <c r="A126" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B126" s="22" t="s">
+      <c r="B126" s="21" t="s">
         <v>260</v>
       </c>
       <c r="C126" s="3" t="s">
@@ -8798,7 +8801,7 @@
       <c r="M126" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N126" s="21" t="s">
+      <c r="N126" s="20" t="s">
         <v>259</v>
       </c>
     </row>
@@ -8834,7 +8837,7 @@
       <c r="J127" s="5">
         <v>2</v>
       </c>
-      <c r="K127" s="12" t="s">
+      <c r="K127" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L127" s="3" t="s">
@@ -8879,7 +8882,7 @@
       <c r="J128" s="5">
         <v>17</v>
       </c>
-      <c r="K128" s="12" t="s">
+      <c r="K128" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L128" s="3" t="s">
@@ -8924,7 +8927,7 @@
       <c r="J129" s="5">
         <v>1</v>
       </c>
-      <c r="K129" s="12" t="s">
+      <c r="K129" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L129" s="3" t="s">
@@ -8969,7 +8972,7 @@
       <c r="J130" s="5">
         <v>1</v>
       </c>
-      <c r="K130" s="12" t="s">
+      <c r="K130" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L130" s="3" t="s">
@@ -9014,7 +9017,7 @@
       <c r="J131" s="5">
         <v>17</v>
       </c>
-      <c r="K131" s="12" t="s">
+      <c r="K131" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L131" s="3" t="s">
@@ -9059,7 +9062,7 @@
       <c r="J132" s="5">
         <v>3</v>
       </c>
-      <c r="K132" s="12" t="s">
+      <c r="K132" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L132" s="3" t="s">
@@ -9104,7 +9107,7 @@
       <c r="J133" s="5">
         <v>0</v>
       </c>
-      <c r="K133" s="12" t="s">
+      <c r="K133" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L133" s="3" t="s">
@@ -9149,7 +9152,7 @@
       <c r="J134" s="5">
         <v>1</v>
       </c>
-      <c r="K134" s="12" t="s">
+      <c r="K134" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L134" s="3" t="s">
@@ -9194,7 +9197,7 @@
       <c r="J135" s="5">
         <v>1</v>
       </c>
-      <c r="K135" s="12" t="s">
+      <c r="K135" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L135" s="3" t="s">
@@ -9239,7 +9242,7 @@
       <c r="J136" s="5">
         <v>0</v>
       </c>
-      <c r="K136" s="12" t="s">
+      <c r="K136" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L136" s="3" t="s">
@@ -9284,7 +9287,7 @@
       <c r="J137" s="5">
         <v>0</v>
       </c>
-      <c r="K137" s="12" t="s">
+      <c r="K137" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L137" s="3" t="s">
@@ -9329,7 +9332,7 @@
       <c r="J138" s="5">
         <v>12</v>
       </c>
-      <c r="K138" s="12" t="s">
+      <c r="K138" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L138" s="3" t="s">
@@ -9374,7 +9377,7 @@
       <c r="J139" s="5">
         <v>7</v>
       </c>
-      <c r="K139" s="12" t="s">
+      <c r="K139" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L139" s="3" t="s">
@@ -9419,7 +9422,7 @@
       <c r="J140" s="5">
         <v>7</v>
       </c>
-      <c r="K140" s="12" t="s">
+      <c r="K140" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L140" s="3" t="s">
@@ -9464,7 +9467,7 @@
       <c r="J141" s="5">
         <v>20</v>
       </c>
-      <c r="K141" s="12" t="s">
+      <c r="K141" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L141" s="3" t="s">
@@ -9509,7 +9512,7 @@
       <c r="J142" s="5">
         <v>28</v>
       </c>
-      <c r="K142" s="12" t="s">
+      <c r="K142" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L142" s="3" t="s">
@@ -9554,7 +9557,7 @@
       <c r="J143" s="5">
         <v>51</v>
       </c>
-      <c r="K143" s="12" t="s">
+      <c r="K143" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L143" s="3" t="s">
@@ -9599,7 +9602,7 @@
       <c r="J144" s="5">
         <v>38</v>
       </c>
-      <c r="K144" s="12" t="s">
+      <c r="K144" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L144" s="3" t="s">
@@ -9644,7 +9647,7 @@
       <c r="J145" s="5">
         <v>14</v>
       </c>
-      <c r="K145" s="12" t="s">
+      <c r="K145" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L145" s="3" t="s">
@@ -9689,7 +9692,7 @@
       <c r="J146" s="5">
         <v>11</v>
       </c>
-      <c r="K146" s="12" t="s">
+      <c r="K146" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L146" s="3" t="s">
@@ -9734,7 +9737,7 @@
       <c r="J147" s="5">
         <v>28</v>
       </c>
-      <c r="K147" s="12" t="s">
+      <c r="K147" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L147" s="3" t="s">
@@ -9779,7 +9782,7 @@
       <c r="J148" s="5">
         <v>23</v>
       </c>
-      <c r="K148" s="12" t="s">
+      <c r="K148" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L148" s="3" t="s">
@@ -9824,7 +9827,7 @@
       <c r="J149" s="5">
         <v>12</v>
       </c>
-      <c r="K149" s="12" t="s">
+      <c r="K149" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L149" s="3" t="s">
@@ -9869,7 +9872,7 @@
       <c r="J150" s="5">
         <v>0</v>
       </c>
-      <c r="K150" s="12" t="s">
+      <c r="K150" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L150" s="3" t="s">
@@ -9914,7 +9917,7 @@
       <c r="J151" s="5">
         <v>0</v>
       </c>
-      <c r="K151" s="12" t="s">
+      <c r="K151" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L151" s="3" t="s">
@@ -9959,7 +9962,7 @@
       <c r="J152" s="5">
         <v>17</v>
       </c>
-      <c r="K152" s="12" t="s">
+      <c r="K152" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L152" s="3" t="s">
@@ -10004,7 +10007,7 @@
       <c r="J153" s="5">
         <v>0</v>
       </c>
-      <c r="K153" s="12" t="s">
+      <c r="K153" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L153" s="3" t="s">
@@ -10049,7 +10052,7 @@
       <c r="J154" s="5">
         <v>0</v>
       </c>
-      <c r="K154" s="12" t="s">
+      <c r="K154" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L154" s="3" t="s">
@@ -10094,7 +10097,7 @@
       <c r="J155" s="5">
         <v>0</v>
       </c>
-      <c r="K155" s="12" t="s">
+      <c r="K155" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L155" s="3" t="s">
@@ -10139,7 +10142,7 @@
       <c r="J156" s="5">
         <v>0</v>
       </c>
-      <c r="K156" s="12" t="s">
+      <c r="K156" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L156" s="3" t="s">
@@ -10184,7 +10187,7 @@
       <c r="J157" s="5">
         <v>1</v>
       </c>
-      <c r="K157" s="12" t="s">
+      <c r="K157" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L157" s="3" t="s">
@@ -10229,7 +10232,7 @@
       <c r="J158" s="5">
         <v>65</v>
       </c>
-      <c r="K158" s="12" t="s">
+      <c r="K158" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L158" s="3" t="s">
@@ -10274,7 +10277,7 @@
       <c r="J159" s="5">
         <v>0</v>
       </c>
-      <c r="K159" s="12" t="s">
+      <c r="K159" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L159" s="3" t="s">
@@ -10319,7 +10322,7 @@
       <c r="J160" s="5">
         <v>13</v>
       </c>
-      <c r="K160" s="12" t="s">
+      <c r="K160" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L160" s="3" t="s">
@@ -10364,7 +10367,7 @@
       <c r="J161" s="5">
         <v>4</v>
       </c>
-      <c r="K161" s="12" t="s">
+      <c r="K161" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L161" s="3" t="s">
@@ -10409,7 +10412,7 @@
       <c r="J162" s="5">
         <v>2</v>
       </c>
-      <c r="K162" s="12" t="s">
+      <c r="K162" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L162" s="3" t="s">
@@ -10454,7 +10457,7 @@
       <c r="J163" s="5">
         <v>1</v>
       </c>
-      <c r="K163" s="12" t="s">
+      <c r="K163" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L163" s="3" t="s">
@@ -10499,7 +10502,7 @@
       <c r="J164" s="5">
         <v>1</v>
       </c>
-      <c r="K164" s="12" t="s">
+      <c r="K164" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L164" s="3" t="s">
@@ -10544,7 +10547,7 @@
       <c r="J165" s="5">
         <v>0</v>
       </c>
-      <c r="K165" s="12" t="s">
+      <c r="K165" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L165" s="3" t="s">
@@ -10589,7 +10592,7 @@
       <c r="J166" s="5">
         <v>2</v>
       </c>
-      <c r="K166" s="12" t="s">
+      <c r="K166" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L166" s="3" t="s">
@@ -10634,7 +10637,7 @@
       <c r="J167" s="5">
         <v>35</v>
       </c>
-      <c r="K167" s="12" t="s">
+      <c r="K167" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L167" s="3" t="s">
@@ -10679,7 +10682,7 @@
       <c r="J168" s="5">
         <v>26</v>
       </c>
-      <c r="K168" s="12" t="s">
+      <c r="K168" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L168" s="3" t="s">
@@ -10724,7 +10727,7 @@
       <c r="J169" s="5">
         <v>33</v>
       </c>
-      <c r="K169" s="12" t="s">
+      <c r="K169" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L169" s="3" t="s">
@@ -10769,7 +10772,7 @@
       <c r="J170" s="5">
         <v>33</v>
       </c>
-      <c r="K170" s="12" t="s">
+      <c r="K170" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L170" s="3" t="s">
@@ -10814,7 +10817,7 @@
       <c r="J171" s="5">
         <v>2</v>
       </c>
-      <c r="K171" s="12" t="s">
+      <c r="K171" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L171" s="3" t="s">
@@ -10859,7 +10862,7 @@
       <c r="J172" s="5">
         <v>3</v>
       </c>
-      <c r="K172" s="12" t="s">
+      <c r="K172" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L172" s="3" t="s">
@@ -10904,7 +10907,7 @@
       <c r="J173" s="5">
         <v>0</v>
       </c>
-      <c r="K173" s="12" t="s">
+      <c r="K173" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L173" s="3" t="s">
@@ -10949,7 +10952,7 @@
       <c r="J174" s="5">
         <v>28</v>
       </c>
-      <c r="K174" s="12" t="s">
+      <c r="K174" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L174" s="3" t="s">
@@ -10994,7 +10997,7 @@
       <c r="J175" s="5">
         <v>14</v>
       </c>
-      <c r="K175" s="12" t="s">
+      <c r="K175" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L175" s="3" t="s">
@@ -11039,7 +11042,7 @@
       <c r="J176" s="5">
         <v>1</v>
       </c>
-      <c r="K176" s="12" t="s">
+      <c r="K176" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L176" s="3" t="s">
@@ -11084,7 +11087,7 @@
       <c r="J177" s="5">
         <v>15</v>
       </c>
-      <c r="K177" s="12" t="s">
+      <c r="K177" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L177" s="3" t="s">
@@ -11129,7 +11132,7 @@
       <c r="J178" s="5">
         <v>16</v>
       </c>
-      <c r="K178" s="12" t="s">
+      <c r="K178" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L178" s="3" t="s">
@@ -11174,7 +11177,7 @@
       <c r="J179" s="5">
         <v>3</v>
       </c>
-      <c r="K179" s="12" t="s">
+      <c r="K179" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L179" s="3" t="s">
@@ -11219,7 +11222,7 @@
       <c r="J180" s="5">
         <v>4</v>
       </c>
-      <c r="K180" s="12" t="s">
+      <c r="K180" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L180" s="3" t="s">
@@ -11264,7 +11267,7 @@
       <c r="J181" s="5">
         <v>22</v>
       </c>
-      <c r="K181" s="12" t="s">
+      <c r="K181" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L181" s="3" t="s">
@@ -11309,7 +11312,7 @@
       <c r="J182" s="5">
         <v>24</v>
       </c>
-      <c r="K182" s="12" t="s">
+      <c r="K182" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L182" s="3" t="s">
@@ -11354,7 +11357,7 @@
       <c r="J183" s="5">
         <v>0</v>
       </c>
-      <c r="K183" s="12" t="s">
+      <c r="K183" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L183" s="3" t="s">
@@ -11399,7 +11402,7 @@
       <c r="J184" s="5">
         <v>59</v>
       </c>
-      <c r="K184" s="12" t="s">
+      <c r="K184" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L184" s="3" t="s">
@@ -11444,7 +11447,7 @@
       <c r="J185" s="5">
         <v>5</v>
       </c>
-      <c r="K185" s="12" t="s">
+      <c r="K185" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L185" s="3" t="s">
@@ -11489,7 +11492,7 @@
       <c r="J186" s="5">
         <v>29</v>
       </c>
-      <c r="K186" s="12" t="s">
+      <c r="K186" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L186" s="3" t="s">
@@ -11534,7 +11537,7 @@
       <c r="J187" s="5">
         <v>2</v>
       </c>
-      <c r="K187" s="12" t="s">
+      <c r="K187" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L187" s="3" t="s">
@@ -11579,7 +11582,7 @@
       <c r="J188" s="5">
         <v>37</v>
       </c>
-      <c r="K188" s="12" t="s">
+      <c r="K188" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L188" s="3" t="s">
@@ -11624,7 +11627,7 @@
       <c r="J189" s="5">
         <v>54</v>
       </c>
-      <c r="K189" s="12" t="s">
+      <c r="K189" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L189" s="3" t="s">
@@ -11669,7 +11672,7 @@
       <c r="J190" s="5">
         <v>5</v>
       </c>
-      <c r="K190" s="12" t="s">
+      <c r="K190" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L190" s="3" t="s">
@@ -11714,7 +11717,7 @@
       <c r="J191" s="5">
         <v>2</v>
       </c>
-      <c r="K191" s="12" t="s">
+      <c r="K191" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L191" s="3" t="s">
@@ -11759,7 +11762,7 @@
       <c r="J192" s="5">
         <v>8</v>
       </c>
-      <c r="K192" s="12" t="s">
+      <c r="K192" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L192" s="3" t="s">
@@ -11804,7 +11807,7 @@
       <c r="J193" s="5">
         <v>39</v>
       </c>
-      <c r="K193" s="12" t="s">
+      <c r="K193" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L193" s="3" t="s">
@@ -11849,7 +11852,7 @@
       <c r="J194" s="5">
         <v>13</v>
       </c>
-      <c r="K194" s="12" t="s">
+      <c r="K194" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L194" s="3" t="s">
@@ -11894,7 +11897,7 @@
       <c r="J195" s="5">
         <v>4</v>
       </c>
-      <c r="K195" s="12" t="s">
+      <c r="K195" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L195" s="3" t="s">
@@ -11939,7 +11942,7 @@
       <c r="J196" s="5">
         <v>13</v>
       </c>
-      <c r="K196" s="12" t="s">
+      <c r="K196" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L196" s="3" t="s">
@@ -11984,7 +11987,7 @@
       <c r="J197" s="5">
         <v>81</v>
       </c>
-      <c r="K197" s="12" t="s">
+      <c r="K197" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L197" s="3" t="s">
@@ -12029,7 +12032,7 @@
       <c r="J198" s="5">
         <v>67</v>
       </c>
-      <c r="K198" s="12" t="s">
+      <c r="K198" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L198" s="3" t="s">
@@ -12074,7 +12077,7 @@
       <c r="J199" s="5">
         <v>64</v>
       </c>
-      <c r="K199" s="12" t="s">
+      <c r="K199" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L199" s="3" t="s">
@@ -12119,7 +12122,7 @@
       <c r="J200" s="5">
         <v>24</v>
       </c>
-      <c r="K200" s="12" t="s">
+      <c r="K200" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L200" s="3" t="s">
@@ -12164,7 +12167,7 @@
       <c r="J201" s="5">
         <v>14</v>
       </c>
-      <c r="K201" s="12" t="s">
+      <c r="K201" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L201" s="3" t="s">
@@ -12209,7 +12212,7 @@
       <c r="J202" s="5">
         <v>9</v>
       </c>
-      <c r="K202" s="12" t="s">
+      <c r="K202" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L202" s="3" t="s">
@@ -12254,7 +12257,7 @@
       <c r="J203" s="5">
         <v>25</v>
       </c>
-      <c r="K203" s="12" t="s">
+      <c r="K203" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L203" s="3" t="s">
@@ -12299,7 +12302,7 @@
       <c r="J204" s="5">
         <v>30</v>
       </c>
-      <c r="K204" s="12" t="s">
+      <c r="K204" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L204" s="3" t="s">
@@ -12344,7 +12347,7 @@
       <c r="J205" s="5">
         <v>1</v>
       </c>
-      <c r="K205" s="12" t="s">
+      <c r="K205" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L205" s="3" t="s">
@@ -12389,7 +12392,7 @@
       <c r="J206" s="5">
         <v>0</v>
       </c>
-      <c r="K206" s="12" t="s">
+      <c r="K206" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L206" s="3" t="s">
@@ -12434,7 +12437,7 @@
       <c r="J207" s="5">
         <v>0</v>
       </c>
-      <c r="K207" s="12" t="s">
+      <c r="K207" s="11" t="s">
         <v>265</v>
       </c>
       <c r="L207" s="3" t="s">
@@ -12653,7 +12656,7 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="I212" s="11" t="s">
+      <c r="I212" s="10" t="s">
         <v>704</v>
       </c>
       <c r="J212" s="5">
@@ -12698,7 +12701,7 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="I213" s="11" t="s">
+      <c r="I213" s="10" t="s">
         <v>707</v>
       </c>
       <c r="J213" s="5">
@@ -12743,7 +12746,7 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="I214" s="11" t="s">
+      <c r="I214" s="10" t="s">
         <v>708</v>
       </c>
       <c r="J214" s="5">
@@ -12758,7 +12761,7 @@
       <c r="M214" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N214" s="21" t="s">
+      <c r="N214" s="20" t="s">
         <v>379</v>
       </c>
     </row>
@@ -12788,7 +12791,7 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="I215" s="11" t="s">
+      <c r="I215" s="10" t="s">
         <v>709</v>
       </c>
       <c r="J215" s="5">
@@ -12804,7 +12807,7 @@
       <c r="M215" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N215" s="21" t="s">
+      <c r="N215" s="20" t="s">
         <v>379</v>
       </c>
     </row>
@@ -12879,7 +12882,7 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="I217" s="11" t="s">
+      <c r="I217" s="10" t="s">
         <v>386</v>
       </c>
       <c r="J217" s="5">
@@ -13014,7 +13017,7 @@
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="I220" s="11" t="s">
+      <c r="I220" s="10" t="s">
         <v>706</v>
       </c>
       <c r="J220" s="5">
@@ -13059,7 +13062,7 @@
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="I221" s="11" t="s">
+      <c r="I221" s="10" t="s">
         <v>710</v>
       </c>
       <c r="J221" s="5">
@@ -13149,7 +13152,7 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="I223" s="11" t="s">
+      <c r="I223" s="10" t="s">
         <v>711</v>
       </c>
       <c r="J223" s="5">
@@ -13194,7 +13197,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I224" s="11" t="s">
+      <c r="I224" s="10" t="s">
         <v>712</v>
       </c>
       <c r="J224" s="5">
@@ -13239,7 +13242,7 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="I225" s="11" t="s">
+      <c r="I225" s="10" t="s">
         <v>713</v>
       </c>
       <c r="J225" s="5">
@@ -13284,7 +13287,7 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="I226" s="11" t="s">
+      <c r="I226" s="10" t="s">
         <v>395</v>
       </c>
       <c r="J226" s="5">
@@ -13329,7 +13332,7 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="I227" s="11" t="s">
+      <c r="I227" s="10" t="s">
         <v>705</v>
       </c>
       <c r="J227" s="5">
@@ -13824,7 +13827,7 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="I238" s="11" t="s">
+      <c r="I238" s="10" t="s">
         <v>714</v>
       </c>
       <c r="J238" s="5">
@@ -13869,7 +13872,7 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="I239" s="11" t="s">
+      <c r="I239" s="10" t="s">
         <v>715</v>
       </c>
       <c r="J239" s="5">
@@ -13914,7 +13917,7 @@
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="I240" s="11" t="s">
+      <c r="I240" s="10" t="s">
         <v>716</v>
       </c>
       <c r="J240" s="5">
@@ -13959,7 +13962,7 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="I241" s="11" t="s">
+      <c r="I241" s="10" t="s">
         <v>411</v>
       </c>
       <c r="J241" s="5">
@@ -14139,7 +14142,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="I245" s="11" t="s">
+      <c r="I245" s="10" t="s">
         <v>717</v>
       </c>
       <c r="J245" s="5">
@@ -14319,7 +14322,7 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="I249" s="11" t="s">
+      <c r="I249" s="10" t="s">
         <v>419</v>
       </c>
       <c r="J249" s="5">
@@ -14364,7 +14367,7 @@
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="I250" s="11" t="s">
+      <c r="I250" s="10" t="s">
         <v>718</v>
       </c>
       <c r="J250" s="5">
@@ -14410,7 +14413,7 @@
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="I251" s="11" t="s">
+      <c r="I251" s="10" t="s">
         <v>422</v>
       </c>
       <c r="J251" s="5">
@@ -15149,11 +15152,11 @@
         <v>438</v>
       </c>
     </row>
-    <row r="268" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="23" t="s">
+    <row r="268" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="B268" s="24" t="s">
+      <c r="B268" s="23" t="s">
         <v>445</v>
       </c>
       <c r="C268" s="3" t="s">
@@ -15162,26 +15165,26 @@
       <c r="D268" s="5">
         <v>44.487842999999998</v>
       </c>
-      <c r="E268" s="15">
+      <c r="E268" s="14">
         <v>12.273384</v>
       </c>
-      <c r="F268" s="12">
+      <c r="F268" s="11">
         <v>1873</v>
       </c>
-      <c r="G268" s="12">
+      <c r="G268" s="11">
         <v>1934</v>
       </c>
       <c r="H268" s="5">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="I268" s="12" t="s">
+      <c r="I268" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="J268" s="15">
+      <c r="J268" s="14">
         <v>12</v>
       </c>
-      <c r="K268" s="12" t="s">
+      <c r="K268" s="11" t="s">
         <v>676</v>
       </c>
       <c r="L268" s="3" t="s">
@@ -15193,20 +15196,20 @@
       <c r="N268" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="O268" s="17"/>
-      <c r="P268" s="17"/>
-      <c r="Q268" s="17"/>
-      <c r="R268" s="17"/>
-      <c r="S268" s="17"/>
-      <c r="T268" s="17"/>
-      <c r="U268" s="17"/>
-      <c r="V268" s="17"/>
-    </row>
-    <row r="269" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="23" t="s">
+      <c r="O268" s="16"/>
+      <c r="P268" s="16"/>
+      <c r="Q268" s="16"/>
+      <c r="R268" s="16"/>
+      <c r="S268" s="16"/>
+      <c r="T268" s="16"/>
+      <c r="U268" s="16"/>
+      <c r="V268" s="16"/>
+    </row>
+    <row r="269" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="B269" s="24" t="s">
+      <c r="B269" s="23" t="s">
         <v>447</v>
       </c>
       <c r="C269" s="3" t="s">
@@ -15215,29 +15218,29 @@
       <c r="D269" s="5">
         <v>44.492660999999998</v>
       </c>
-      <c r="E269" s="15">
+      <c r="E269" s="14">
         <v>12.286345000000001</v>
       </c>
-      <c r="F269" s="12">
+      <c r="F269" s="11">
         <v>1934</v>
       </c>
-      <c r="G269" s="12">
+      <c r="G269" s="11">
         <v>1957</v>
       </c>
       <c r="H269" s="5">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="I269" s="12" t="s">
+      <c r="I269" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="J269" s="15">
+      <c r="J269" s="14">
         <v>3</v>
       </c>
-      <c r="K269" s="12" t="s">
+      <c r="K269" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="L269" s="12" t="s">
+      <c r="L269" s="11" t="s">
         <v>32</v>
       </c>
       <c r="M269" s="3" t="s">
@@ -15246,20 +15249,20 @@
       <c r="N269" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="O269" s="17"/>
-      <c r="P269" s="17"/>
-      <c r="Q269" s="17"/>
-      <c r="R269" s="17"/>
-      <c r="S269" s="17"/>
-      <c r="T269" s="17"/>
-      <c r="U269" s="17"/>
-      <c r="V269" s="17"/>
-    </row>
-    <row r="270" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="23" t="s">
+      <c r="O269" s="16"/>
+      <c r="P269" s="16"/>
+      <c r="Q269" s="16"/>
+      <c r="R269" s="16"/>
+      <c r="S269" s="16"/>
+      <c r="T269" s="16"/>
+      <c r="U269" s="16"/>
+      <c r="V269" s="16"/>
+    </row>
+    <row r="270" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="22" t="s">
         <v>444</v>
       </c>
-      <c r="B270" s="24" t="s">
+      <c r="B270" s="23" t="s">
         <v>448</v>
       </c>
       <c r="C270" s="3" t="s">
@@ -15268,29 +15271,29 @@
       <c r="D270" s="5">
         <v>44.492125999999999</v>
       </c>
-      <c r="E270" s="15">
+      <c r="E270" s="14">
         <v>12.283148000000001</v>
       </c>
-      <c r="F270" s="12">
+      <c r="F270" s="11">
         <v>1957</v>
       </c>
-      <c r="G270" s="12">
+      <c r="G270" s="11">
         <v>1986</v>
       </c>
       <c r="H270" s="5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="I270" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J270" s="15">
+      <c r="I270" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J270" s="14">
         <v>0</v>
       </c>
-      <c r="K270" s="12" t="s">
+      <c r="K270" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="L270" s="12" t="s">
+      <c r="L270" s="11" t="s">
         <v>32</v>
       </c>
       <c r="M270" s="3" t="s">
@@ -15299,17 +15302,17 @@
       <c r="N270" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="O270" s="17"/>
-      <c r="P270" s="17"/>
-      <c r="Q270" s="17"/>
-      <c r="R270" s="17"/>
-      <c r="S270" s="17"/>
-      <c r="T270" s="17"/>
-      <c r="U270" s="17"/>
-      <c r="V270" s="17"/>
-    </row>
-    <row r="271" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="23" t="s">
+      <c r="O270" s="16"/>
+      <c r="P270" s="16"/>
+      <c r="Q270" s="16"/>
+      <c r="R270" s="16"/>
+      <c r="S270" s="16"/>
+      <c r="T270" s="16"/>
+      <c r="U270" s="16"/>
+      <c r="V270" s="16"/>
+    </row>
+    <row r="271" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="22" t="s">
         <v>449</v>
       </c>
       <c r="B271" s="3" t="s">
@@ -15324,26 +15327,26 @@
       <c r="E271" s="5">
         <v>-66.982954000000007</v>
       </c>
-      <c r="F271" s="12">
+      <c r="F271" s="11">
         <v>1860</v>
       </c>
-      <c r="G271" s="12">
+      <c r="G271" s="11">
         <v>1890</v>
       </c>
       <c r="H271" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="I271" s="12" t="s">
+      <c r="I271" s="11" t="s">
         <v>723</v>
       </c>
-      <c r="J271" s="15">
+      <c r="J271" s="14">
         <v>24</v>
       </c>
-      <c r="K271" s="12" t="s">
+      <c r="K271" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="L271" s="12" t="s">
+      <c r="L271" s="11" t="s">
         <v>32</v>
       </c>
       <c r="M271" s="3" t="s">
@@ -15352,20 +15355,20 @@
       <c r="N271" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="O271" s="17"/>
-      <c r="P271" s="17"/>
-      <c r="Q271" s="17"/>
-      <c r="R271" s="17"/>
-      <c r="S271" s="17"/>
-      <c r="T271" s="17"/>
-      <c r="U271" s="17"/>
-      <c r="V271" s="17"/>
-    </row>
-    <row r="272" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="23" t="s">
+      <c r="O271" s="16"/>
+      <c r="P271" s="16"/>
+      <c r="Q271" s="16"/>
+      <c r="R271" s="16"/>
+      <c r="S271" s="16"/>
+      <c r="T271" s="16"/>
+      <c r="U271" s="16"/>
+      <c r="V271" s="16"/>
+    </row>
+    <row r="272" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="22" t="s">
         <v>449</v>
       </c>
-      <c r="B272" s="24" t="s">
+      <c r="B272" s="23" t="s">
         <v>416</v>
       </c>
       <c r="C272" s="3" t="s">
@@ -15377,26 +15380,26 @@
       <c r="E272" s="5">
         <v>-70.244313000000005</v>
       </c>
-      <c r="F272" s="12">
+      <c r="F272" s="11">
         <v>1864</v>
       </c>
-      <c r="G272" s="12">
+      <c r="G272" s="11">
         <v>1866</v>
       </c>
       <c r="H272" s="5">
         <f t="shared" ref="H272:H339" si="2">(1+(G272-F272))-J272</f>
         <v>1.42</v>
       </c>
-      <c r="I272" s="12" t="s">
+      <c r="I272" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="J272" s="15">
+      <c r="J272" s="14">
         <v>1.58</v>
       </c>
-      <c r="K272" s="12" t="s">
+      <c r="K272" s="11" t="s">
         <v>676</v>
       </c>
-      <c r="L272" s="12" t="s">
+      <c r="L272" s="11" t="s">
         <v>32</v>
       </c>
       <c r="M272" s="3" t="s">
@@ -15405,17 +15408,17 @@
       <c r="N272" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="O272" s="17"/>
-      <c r="P272" s="17"/>
-      <c r="Q272" s="17"/>
-      <c r="R272" s="17"/>
-      <c r="S272" s="17"/>
-      <c r="T272" s="17"/>
-      <c r="U272" s="17"/>
-      <c r="V272" s="17"/>
-    </row>
-    <row r="273" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="23" t="s">
+      <c r="O272" s="16"/>
+      <c r="P272" s="16"/>
+      <c r="Q272" s="16"/>
+      <c r="R272" s="16"/>
+      <c r="S272" s="16"/>
+      <c r="T272" s="16"/>
+      <c r="U272" s="16"/>
+      <c r="V272" s="16"/>
+    </row>
+    <row r="273" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="22" t="s">
         <v>449</v>
       </c>
       <c r="B273" s="3" t="s">
@@ -15440,16 +15443,16 @@
         <f t="shared" si="2"/>
         <v>8.9000000000000057</v>
       </c>
-      <c r="I273" s="12" t="s">
+      <c r="I273" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="J273" s="15">
+      <c r="J273" s="14">
         <v>68.099999999999994</v>
       </c>
-      <c r="K273" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L273" s="12" t="s">
+      <c r="K273" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L273" s="11" t="s">
         <v>32</v>
       </c>
       <c r="M273" s="3" t="s">
@@ -15458,14 +15461,14 @@
       <c r="N273" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="O273" s="17"/>
-      <c r="P273" s="17"/>
-      <c r="Q273" s="17"/>
-      <c r="R273" s="17"/>
-      <c r="S273" s="17"/>
-      <c r="T273" s="17"/>
-      <c r="U273" s="17"/>
-      <c r="V273" s="17"/>
+      <c r="O273" s="16"/>
+      <c r="P273" s="16"/>
+      <c r="Q273" s="16"/>
+      <c r="R273" s="16"/>
+      <c r="S273" s="16"/>
+      <c r="T273" s="16"/>
+      <c r="U273" s="16"/>
+      <c r="V273" s="16"/>
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
@@ -15493,13 +15496,13 @@
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="I274" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J274" s="15">
+      <c r="I274" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J274" s="14">
         <v>0</v>
       </c>
-      <c r="K274" s="12" t="s">
+      <c r="K274" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L274" s="3" t="s">
@@ -15538,13 +15541,13 @@
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="I275" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J275" s="15">
+      <c r="I275" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J275" s="14">
         <v>0</v>
       </c>
-      <c r="K275" s="12" t="s">
+      <c r="K275" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L275" s="3" t="s">
@@ -15583,13 +15586,13 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="I276" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J276" s="15">
+      <c r="I276" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J276" s="14">
         <v>0</v>
       </c>
-      <c r="K276" s="12" t="s">
+      <c r="K276" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L276" s="3" t="s">
@@ -15628,13 +15631,13 @@
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="I277" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J277" s="15">
+      <c r="I277" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J277" s="14">
         <v>0</v>
       </c>
-      <c r="K277" s="12" t="s">
+      <c r="K277" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L277" s="3" t="s">
@@ -15673,13 +15676,13 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="I278" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J278" s="15">
+      <c r="I278" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J278" s="14">
         <v>0</v>
       </c>
-      <c r="K278" s="12" t="s">
+      <c r="K278" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L278" s="3" t="s">
@@ -15718,13 +15721,13 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="I279" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J279" s="15">
+      <c r="I279" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J279" s="14">
         <v>0</v>
       </c>
-      <c r="K279" s="12" t="s">
+      <c r="K279" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L279" s="3" t="s">
@@ -15763,13 +15766,13 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="I280" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J280" s="15">
+      <c r="I280" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J280" s="14">
         <v>0</v>
       </c>
-      <c r="K280" s="12" t="s">
+      <c r="K280" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L280" s="3" t="s">
@@ -15808,13 +15811,13 @@
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
-      <c r="I281" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J281" s="15">
+      <c r="I281" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J281" s="14">
         <v>0</v>
       </c>
-      <c r="K281" s="12" t="s">
+      <c r="K281" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L281" s="3" t="s">
@@ -15853,13 +15856,13 @@
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="I282" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J282" s="15">
+      <c r="I282" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J282" s="14">
         <v>0</v>
       </c>
-      <c r="K282" s="12" t="s">
+      <c r="K282" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L282" s="3" t="s">
@@ -15898,13 +15901,13 @@
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="I283" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J283" s="15">
+      <c r="I283" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J283" s="14">
         <v>0</v>
       </c>
-      <c r="K283" s="12" t="s">
+      <c r="K283" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L283" s="3" t="s">
@@ -15943,13 +15946,13 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="I284" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J284" s="15">
+      <c r="I284" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J284" s="14">
         <v>0</v>
       </c>
-      <c r="K284" s="12" t="s">
+      <c r="K284" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L284" s="3" t="s">
@@ -15988,13 +15991,13 @@
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="I285" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J285" s="15">
+      <c r="I285" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J285" s="14">
         <v>0</v>
       </c>
-      <c r="K285" s="12" t="s">
+      <c r="K285" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L285" s="3" t="s">
@@ -16033,13 +16036,13 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="I286" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J286" s="15">
+      <c r="I286" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J286" s="14">
         <v>0</v>
       </c>
-      <c r="K286" s="12" t="s">
+      <c r="K286" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L286" s="3" t="s">
@@ -16078,13 +16081,13 @@
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="I287" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J287" s="15">
+      <c r="I287" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J287" s="14">
         <v>0</v>
       </c>
-      <c r="K287" s="12" t="s">
+      <c r="K287" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L287" s="3" t="s">
@@ -16123,13 +16126,13 @@
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="I288" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J288" s="15">
+      <c r="I288" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J288" s="14">
         <v>0</v>
       </c>
-      <c r="K288" s="12" t="s">
+      <c r="K288" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L288" s="3" t="s">
@@ -16168,13 +16171,13 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="I289" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J289" s="15">
+      <c r="I289" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J289" s="14">
         <v>0</v>
       </c>
-      <c r="K289" s="12" t="s">
+      <c r="K289" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L289" s="3" t="s">
@@ -16213,13 +16216,13 @@
         <f t="shared" si="2"/>
         <v>187</v>
       </c>
-      <c r="I290" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J290" s="15">
+      <c r="I290" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J290" s="14">
         <v>0</v>
       </c>
-      <c r="K290" s="12" t="s">
+      <c r="K290" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L290" s="3" t="s">
@@ -16258,13 +16261,13 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="I291" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J291" s="15">
+      <c r="I291" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J291" s="14">
         <v>0</v>
       </c>
-      <c r="K291" s="12" t="s">
+      <c r="K291" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L291" s="3" t="s">
@@ -16303,13 +16306,13 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="I292" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J292" s="15">
+      <c r="I292" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J292" s="14">
         <v>0</v>
       </c>
-      <c r="K292" s="12" t="s">
+      <c r="K292" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L292" s="3" t="s">
@@ -16348,13 +16351,13 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="I293" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J293" s="15">
+      <c r="I293" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J293" s="14">
         <v>0</v>
       </c>
-      <c r="K293" s="12" t="s">
+      <c r="K293" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L293" s="3" t="s">
@@ -16393,13 +16396,13 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="I294" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J294" s="15">
+      <c r="I294" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J294" s="14">
         <v>0</v>
       </c>
-      <c r="K294" s="12" t="s">
+      <c r="K294" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L294" s="3" t="s">
@@ -16438,13 +16441,13 @@
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
-      <c r="I295" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J295" s="15">
+      <c r="I295" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J295" s="14">
         <v>0</v>
       </c>
-      <c r="K295" s="12" t="s">
+      <c r="K295" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L295" s="3" t="s">
@@ -16483,13 +16486,13 @@
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="I296" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J296" s="15">
+      <c r="I296" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J296" s="14">
         <v>0</v>
       </c>
-      <c r="K296" s="12" t="s">
+      <c r="K296" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L296" s="3" t="s">
@@ -16528,13 +16531,13 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="I297" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J297" s="15">
+      <c r="I297" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J297" s="14">
         <v>0</v>
       </c>
-      <c r="K297" s="12" t="s">
+      <c r="K297" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L297" s="3" t="s">
@@ -16573,13 +16576,13 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="I298" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J298" s="15">
+      <c r="I298" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J298" s="14">
         <v>0</v>
       </c>
-      <c r="K298" s="12" t="s">
+      <c r="K298" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L298" s="3" t="s">
@@ -16618,13 +16621,13 @@
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="I299" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J299" s="15">
+      <c r="I299" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J299" s="14">
         <v>0</v>
       </c>
-      <c r="K299" s="12" t="s">
+      <c r="K299" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L299" s="3" t="s">
@@ -16663,13 +16666,13 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="I300" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J300" s="15">
+      <c r="I300" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J300" s="14">
         <v>0</v>
       </c>
-      <c r="K300" s="12" t="s">
+      <c r="K300" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L300" s="3" t="s">
@@ -16708,13 +16711,13 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="I301" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J301" s="15">
+      <c r="I301" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J301" s="14">
         <v>0</v>
       </c>
-      <c r="K301" s="12" t="s">
+      <c r="K301" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L301" s="3" t="s">
@@ -16753,13 +16756,13 @@
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="I302" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J302" s="15">
+      <c r="I302" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J302" s="14">
         <v>0</v>
       </c>
-      <c r="K302" s="12" t="s">
+      <c r="K302" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L302" s="3" t="s">
@@ -16798,13 +16801,13 @@
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="I303" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J303" s="15">
+      <c r="I303" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J303" s="14">
         <v>0</v>
       </c>
-      <c r="K303" s="12" t="s">
+      <c r="K303" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L303" s="3" t="s">
@@ -16843,13 +16846,13 @@
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="I304" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J304" s="15">
+      <c r="I304" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J304" s="14">
         <v>0</v>
       </c>
-      <c r="K304" s="12" t="s">
+      <c r="K304" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L304" s="3" t="s">
@@ -16888,13 +16891,13 @@
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="I305" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J305" s="15">
+      <c r="I305" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J305" s="14">
         <v>0</v>
       </c>
-      <c r="K305" s="12" t="s">
+      <c r="K305" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L305" s="3" t="s">
@@ -16933,13 +16936,13 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="I306" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J306" s="15">
+      <c r="I306" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J306" s="14">
         <v>0</v>
       </c>
-      <c r="K306" s="12" t="s">
+      <c r="K306" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L306" s="3" t="s">
@@ -16978,13 +16981,13 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="I307" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J307" s="15">
+      <c r="I307" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J307" s="14">
         <v>0</v>
       </c>
-      <c r="K307" s="12" t="s">
+      <c r="K307" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L307" s="3" t="s">
@@ -17023,13 +17026,13 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="I308" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J308" s="15">
+      <c r="I308" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J308" s="14">
         <v>0</v>
       </c>
-      <c r="K308" s="12" t="s">
+      <c r="K308" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L308" s="3" t="s">
@@ -17068,13 +17071,13 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="I309" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J309" s="15">
+      <c r="I309" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J309" s="14">
         <v>0</v>
       </c>
-      <c r="K309" s="12" t="s">
+      <c r="K309" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L309" s="3" t="s">
@@ -17113,13 +17116,13 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="I310" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J310" s="15">
+      <c r="I310" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J310" s="14">
         <v>0</v>
       </c>
-      <c r="K310" s="12" t="s">
+      <c r="K310" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L310" s="3" t="s">
@@ -17158,13 +17161,13 @@
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="I311" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J311" s="15">
+      <c r="I311" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J311" s="14">
         <v>0</v>
       </c>
-      <c r="K311" s="12" t="s">
+      <c r="K311" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L311" s="3" t="s">
@@ -17203,13 +17206,13 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="I312" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J312" s="15">
+      <c r="I312" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J312" s="14">
         <v>0</v>
       </c>
-      <c r="K312" s="12" t="s">
+      <c r="K312" s="11" t="s">
         <v>249</v>
       </c>
       <c r="L312" s="3" t="s">
@@ -17248,10 +17251,10 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I313" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J313" s="15">
+      <c r="I313" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J313" s="14">
         <v>0</v>
       </c>
       <c r="K313" s="3" t="s">
@@ -17293,7 +17296,7 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="I314" s="11" t="s">
+      <c r="I314" s="10" t="s">
         <v>724</v>
       </c>
       <c r="J314" s="5">
@@ -17383,7 +17386,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I316" s="11" t="s">
+      <c r="I316" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J316" s="5">
@@ -17428,7 +17431,7 @@
         <f>(1+(G317-F317))-J317</f>
         <v>7</v>
       </c>
-      <c r="I317" s="11" t="s">
+      <c r="I317" s="10" t="s">
         <v>725</v>
       </c>
       <c r="J317" s="5">
@@ -17518,7 +17521,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I319" s="11" t="s">
+      <c r="I319" s="10" t="s">
         <v>726</v>
       </c>
       <c r="J319" s="5">
@@ -17564,7 +17567,7 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I320" s="11" t="s">
+      <c r="I320" s="10" t="s">
         <v>727</v>
       </c>
       <c r="J320" s="5">
@@ -17609,7 +17612,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I321" s="11" t="s">
+      <c r="I321" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J321" s="5">
@@ -17654,7 +17657,7 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="I322" s="11" t="s">
+      <c r="I322" s="10" t="s">
         <v>728</v>
       </c>
       <c r="J322" s="5">
@@ -17700,7 +17703,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I323" s="11" t="s">
+      <c r="I323" s="10" t="s">
         <v>729</v>
       </c>
       <c r="J323" s="5">
@@ -17745,7 +17748,7 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="I324" s="11" t="s">
+      <c r="I324" s="10" t="s">
         <v>730</v>
       </c>
       <c r="J324" s="5">
@@ -17791,7 +17794,7 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I325" s="11" t="s">
+      <c r="I325" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J325" s="5">
@@ -17836,7 +17839,7 @@
         <f t="shared" si="2"/>
         <v>47.917864476386036</v>
       </c>
-      <c r="I326" s="11" t="s">
+      <c r="I326" s="10" t="s">
         <v>731</v>
       </c>
       <c r="J326" s="5">
@@ -17906,7 +17909,7 @@
       <c r="A328" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="B328" s="24" t="s">
+      <c r="B328" s="23" t="s">
         <v>512</v>
       </c>
       <c r="C328" s="3" t="s">
@@ -18018,7 +18021,7 @@
         <f t="shared" si="2"/>
         <v>44</v>
       </c>
-      <c r="I330" s="11" t="s">
+      <c r="I330" s="10" t="s">
         <v>733</v>
       </c>
       <c r="J330" s="5">
@@ -18153,7 +18156,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I333" s="11" t="s">
+      <c r="I333" s="10" t="s">
         <v>734</v>
       </c>
       <c r="J333" s="5">
@@ -18198,7 +18201,7 @@
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="I334" s="11" t="s">
+      <c r="I334" s="10" t="s">
         <v>735</v>
       </c>
       <c r="J334" s="5">
@@ -18243,7 +18246,7 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="I335" s="11">
+      <c r="I335" s="10">
         <v>1955</v>
       </c>
       <c r="J335" s="5">
@@ -18262,7 +18265,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="336" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>525</v>
       </c>
@@ -18288,7 +18291,7 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I336" s="11" t="s">
+      <c r="I336" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J336" s="5">
@@ -18306,16 +18309,16 @@
       <c r="N336" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="O336" s="17"/>
-      <c r="P336" s="17"/>
-      <c r="Q336" s="17"/>
-      <c r="R336" s="17"/>
-      <c r="S336" s="17"/>
-      <c r="T336" s="17"/>
-      <c r="U336" s="17"/>
-      <c r="V336" s="17"/>
-    </row>
-    <row r="337" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O336" s="16"/>
+      <c r="P336" s="16"/>
+      <c r="Q336" s="16"/>
+      <c r="R336" s="16"/>
+      <c r="S336" s="16"/>
+      <c r="T336" s="16"/>
+      <c r="U336" s="16"/>
+      <c r="V336" s="16"/>
+    </row>
+    <row r="337" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>525</v>
       </c>
@@ -18341,7 +18344,7 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I337" s="11" t="s">
+      <c r="I337" s="10" t="s">
         <v>16</v>
       </c>
       <c r="J337" s="5">
@@ -18359,16 +18362,16 @@
       <c r="N337" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="O337" s="17"/>
-      <c r="P337" s="17"/>
-      <c r="Q337" s="17"/>
-      <c r="R337" s="17"/>
-      <c r="S337" s="17"/>
-      <c r="T337" s="17"/>
-      <c r="U337" s="17"/>
-      <c r="V337" s="17"/>
-    </row>
-    <row r="338" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O337" s="16"/>
+      <c r="P337" s="16"/>
+      <c r="Q337" s="16"/>
+      <c r="R337" s="16"/>
+      <c r="S337" s="16"/>
+      <c r="T337" s="16"/>
+      <c r="U337" s="16"/>
+      <c r="V337" s="16"/>
+    </row>
+    <row r="338" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>525</v>
       </c>
@@ -18394,7 +18397,7 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I338" s="11" t="s">
+      <c r="I338" s="10" t="s">
         <v>737</v>
       </c>
       <c r="J338" s="5">
@@ -18412,16 +18415,16 @@
       <c r="N338" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="O338" s="17"/>
-      <c r="P338" s="17"/>
-      <c r="Q338" s="17"/>
-      <c r="R338" s="17"/>
-      <c r="S338" s="17"/>
-      <c r="T338" s="17"/>
-      <c r="U338" s="17"/>
-      <c r="V338" s="17"/>
-    </row>
-    <row r="339" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O338" s="16"/>
+      <c r="P338" s="16"/>
+      <c r="Q338" s="16"/>
+      <c r="R338" s="16"/>
+      <c r="S338" s="16"/>
+      <c r="T338" s="16"/>
+      <c r="U338" s="16"/>
+      <c r="V338" s="16"/>
+    </row>
+    <row r="339" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>525</v>
       </c>
@@ -18447,7 +18450,7 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I339" s="11" t="s">
+      <c r="I339" s="10" t="s">
         <v>736</v>
       </c>
       <c r="J339" s="5">
@@ -18465,16 +18468,16 @@
       <c r="N339" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="O339" s="17"/>
-      <c r="P339" s="17"/>
-      <c r="Q339" s="17"/>
-      <c r="R339" s="17"/>
-      <c r="S339" s="17"/>
-      <c r="T339" s="17"/>
-      <c r="U339" s="17"/>
-      <c r="V339" s="17"/>
-    </row>
-    <row r="340" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O339" s="16"/>
+      <c r="P339" s="16"/>
+      <c r="Q339" s="16"/>
+      <c r="R339" s="16"/>
+      <c r="S339" s="16"/>
+      <c r="T339" s="16"/>
+      <c r="U339" s="16"/>
+      <c r="V339" s="16"/>
+    </row>
+    <row r="340" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>531</v>
       </c>
@@ -18518,16 +18521,16 @@
       <c r="N340" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="O340" s="17"/>
-      <c r="P340" s="17"/>
-      <c r="Q340" s="17"/>
-      <c r="R340" s="17"/>
-      <c r="S340" s="17"/>
-      <c r="T340" s="17"/>
-      <c r="U340" s="17"/>
-      <c r="V340" s="17"/>
-    </row>
-    <row r="341" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="O340" s="16"/>
+      <c r="P340" s="16"/>
+      <c r="Q340" s="16"/>
+      <c r="R340" s="16"/>
+      <c r="S340" s="16"/>
+      <c r="T340" s="16"/>
+      <c r="U340" s="16"/>
+      <c r="V340" s="16"/>
+    </row>
+    <row r="341" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>531</v>
       </c>
@@ -18571,20 +18574,20 @@
       <c r="N341" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="O341" s="17"/>
-      <c r="P341" s="17"/>
-      <c r="Q341" s="17"/>
-      <c r="R341" s="17"/>
-      <c r="S341" s="17"/>
-      <c r="T341" s="17"/>
-      <c r="U341" s="17"/>
-      <c r="V341" s="17"/>
-    </row>
-    <row r="342" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A342" s="25" t="s">
+      <c r="O341" s="16"/>
+      <c r="P341" s="16"/>
+      <c r="Q341" s="16"/>
+      <c r="R341" s="16"/>
+      <c r="S341" s="16"/>
+      <c r="T341" s="16"/>
+      <c r="U341" s="16"/>
+      <c r="V341" s="16"/>
+    </row>
+    <row r="342" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A342" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B342" s="26" t="s">
+      <c r="B342" s="25" t="s">
         <v>536</v>
       </c>
       <c r="C342" s="3" t="s">
@@ -18596,20 +18599,20 @@
       <c r="E342" s="5">
         <v>8.9</v>
       </c>
-      <c r="F342" s="12">
+      <c r="F342" s="11">
         <v>1884</v>
       </c>
-      <c r="G342" s="12">
+      <c r="G342" s="11">
         <v>2014</v>
       </c>
       <c r="H342" s="5">
         <f t="shared" si="3"/>
         <v>102.7433</v>
       </c>
-      <c r="I342" s="12" t="s">
+      <c r="I342" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J342" s="15">
+      <c r="J342" s="14">
         <f>(1+(G342-F342))*0.2157</f>
         <v>28.256700000000002</v>
       </c>
@@ -18619,26 +18622,26 @@
       <c r="L342" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M342" s="12" t="s">
+      <c r="M342" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N342" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O342" s="17"/>
-      <c r="P342" s="17"/>
-      <c r="Q342" s="17"/>
-      <c r="R342" s="17"/>
-      <c r="S342" s="17"/>
-      <c r="T342" s="17"/>
-      <c r="U342" s="17"/>
-      <c r="V342" s="17"/>
-    </row>
-    <row r="343" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A343" s="25" t="s">
+      <c r="O342" s="16"/>
+      <c r="P342" s="16"/>
+      <c r="Q342" s="16"/>
+      <c r="R342" s="16"/>
+      <c r="S342" s="16"/>
+      <c r="T342" s="16"/>
+      <c r="U342" s="16"/>
+      <c r="V342" s="16"/>
+    </row>
+    <row r="343" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A343" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B343" s="24" t="s">
+      <c r="B343" s="23" t="s">
         <v>538</v>
       </c>
       <c r="C343" s="3" t="s">
@@ -18650,20 +18653,20 @@
       <c r="E343" s="5">
         <v>-5.43</v>
       </c>
-      <c r="F343" s="12">
+      <c r="F343" s="11">
         <v>1943</v>
       </c>
-      <c r="G343" s="12">
+      <c r="G343" s="11">
         <v>2018</v>
       </c>
       <c r="H343" s="5">
         <f t="shared" si="3"/>
         <v>61.1496</v>
       </c>
-      <c r="I343" s="12" t="s">
+      <c r="I343" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J343" s="15">
+      <c r="J343" s="14">
         <f>(1+(G343-F343))*0.1954</f>
         <v>14.850399999999999</v>
       </c>
@@ -18673,26 +18676,26 @@
       <c r="L343" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M343" s="12" t="s">
+      <c r="M343" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N343" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O343" s="17"/>
-      <c r="P343" s="17"/>
-      <c r="Q343" s="17"/>
-      <c r="R343" s="17"/>
-      <c r="S343" s="17"/>
-      <c r="T343" s="17"/>
-      <c r="U343" s="17"/>
-      <c r="V343" s="17"/>
-    </row>
-    <row r="344" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A344" s="25" t="s">
+      <c r="O343" s="16"/>
+      <c r="P343" s="16"/>
+      <c r="Q343" s="16"/>
+      <c r="R343" s="16"/>
+      <c r="S343" s="16"/>
+      <c r="T343" s="16"/>
+      <c r="U343" s="16"/>
+      <c r="V343" s="16"/>
+    </row>
+    <row r="344" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A344" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B344" s="24" t="s">
+      <c r="B344" s="23" t="s">
         <v>539</v>
       </c>
       <c r="C344" s="3" t="s">
@@ -18704,20 +18707,20 @@
       <c r="E344" s="5">
         <v>9.17</v>
       </c>
-      <c r="F344" s="12">
+      <c r="F344" s="11">
         <v>1896</v>
       </c>
-      <c r="G344" s="12">
+      <c r="G344" s="11">
         <v>2014</v>
       </c>
       <c r="H344" s="5">
         <f t="shared" si="3"/>
         <v>50.325100000000006</v>
       </c>
-      <c r="I344" s="12" t="s">
+      <c r="I344" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J344" s="15">
+      <c r="J344" s="14">
         <f>(1+(G344-F344))*0.5771</f>
         <v>68.674899999999994</v>
       </c>
@@ -18727,26 +18730,26 @@
       <c r="L344" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M344" s="12" t="s">
+      <c r="M344" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N344" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O344" s="17"/>
-      <c r="P344" s="17"/>
-      <c r="Q344" s="17"/>
-      <c r="R344" s="17"/>
-      <c r="S344" s="17"/>
-      <c r="T344" s="17"/>
-      <c r="U344" s="17"/>
-      <c r="V344" s="17"/>
-    </row>
-    <row r="345" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A345" s="25" t="s">
+      <c r="O344" s="16"/>
+      <c r="P344" s="16"/>
+      <c r="Q344" s="16"/>
+      <c r="R344" s="16"/>
+      <c r="S344" s="16"/>
+      <c r="T344" s="16"/>
+      <c r="U344" s="16"/>
+      <c r="V344" s="16"/>
+    </row>
+    <row r="345" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A345" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B345" s="24" t="s">
+      <c r="B345" s="23" t="s">
         <v>540</v>
       </c>
       <c r="C345" s="3" t="s">
@@ -18755,23 +18758,23 @@
       <c r="D345" s="5">
         <v>35.89</v>
       </c>
-      <c r="E345" s="15">
+      <c r="E345" s="14">
         <v>-5.32</v>
       </c>
-      <c r="F345" s="12">
+      <c r="F345" s="11">
         <v>1944</v>
       </c>
-      <c r="G345" s="12">
+      <c r="G345" s="11">
         <v>2018</v>
       </c>
       <c r="H345" s="5">
         <f t="shared" si="3"/>
         <v>72.540000000000006</v>
       </c>
-      <c r="I345" s="12" t="s">
+      <c r="I345" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J345" s="15">
+      <c r="J345" s="14">
         <f>(1+(G345-F345))*0.0328</f>
         <v>2.4600000000000004</v>
       </c>
@@ -18781,26 +18784,26 @@
       <c r="L345" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M345" s="12" t="s">
+      <c r="M345" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N345" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O345" s="17"/>
-      <c r="P345" s="17"/>
-      <c r="Q345" s="17"/>
-      <c r="R345" s="17"/>
-      <c r="S345" s="17"/>
-      <c r="T345" s="17"/>
-      <c r="U345" s="17"/>
-      <c r="V345" s="17"/>
-    </row>
-    <row r="346" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A346" s="25" t="s">
+      <c r="O345" s="16"/>
+      <c r="P345" s="16"/>
+      <c r="Q345" s="16"/>
+      <c r="R345" s="16"/>
+      <c r="S345" s="16"/>
+      <c r="T345" s="16"/>
+      <c r="U345" s="16"/>
+      <c r="V345" s="16"/>
+    </row>
+    <row r="346" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A346" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B346" s="24" t="s">
+      <c r="B346" s="23" t="s">
         <v>541</v>
       </c>
       <c r="C346" s="3" t="s">
@@ -18809,23 +18812,23 @@
       <c r="D346" s="5">
         <v>36.71</v>
       </c>
-      <c r="E346" s="15">
+      <c r="E346" s="14">
         <v>-4.42</v>
       </c>
-      <c r="F346" s="12">
+      <c r="F346" s="11">
         <v>1944</v>
       </c>
-      <c r="G346" s="12">
+      <c r="G346" s="11">
         <v>2018</v>
       </c>
       <c r="H346" s="5">
         <f t="shared" si="3"/>
         <v>62.67</v>
       </c>
-      <c r="I346" s="12" t="s">
+      <c r="I346" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J346" s="15">
+      <c r="J346" s="14">
         <f>(1+(G346-F346))*0.1644</f>
         <v>12.33</v>
       </c>
@@ -18835,26 +18838,26 @@
       <c r="L346" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M346" s="12" t="s">
+      <c r="M346" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N346" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O346" s="17"/>
-      <c r="P346" s="17"/>
-      <c r="Q346" s="17"/>
-      <c r="R346" s="17"/>
-      <c r="S346" s="17"/>
-      <c r="T346" s="17"/>
-      <c r="U346" s="17"/>
-      <c r="V346" s="17"/>
-    </row>
-    <row r="347" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A347" s="25" t="s">
+      <c r="O346" s="16"/>
+      <c r="P346" s="16"/>
+      <c r="Q346" s="16"/>
+      <c r="R346" s="16"/>
+      <c r="S346" s="16"/>
+      <c r="T346" s="16"/>
+      <c r="U346" s="16"/>
+      <c r="V346" s="16"/>
+    </row>
+    <row r="347" spans="1:22" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A347" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B347" s="24" t="s">
+      <c r="B347" s="23" t="s">
         <v>542</v>
       </c>
       <c r="C347" s="3" t="s">
@@ -18866,20 +18869,20 @@
       <c r="E347" s="5">
         <v>7.42</v>
       </c>
-      <c r="F347" s="12">
+      <c r="F347" s="11">
         <v>1956</v>
       </c>
-      <c r="G347" s="12">
+      <c r="G347" s="11">
         <v>2019</v>
       </c>
       <c r="H347" s="5">
         <f t="shared" si="3"/>
         <v>33.177599999999998</v>
       </c>
-      <c r="I347" s="12" t="s">
+      <c r="I347" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J347" s="15">
+      <c r="J347" s="14">
         <f>(1+(G347-F347))*0.4816</f>
         <v>30.822399999999998</v>
       </c>
@@ -18889,26 +18892,26 @@
       <c r="L347" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M347" s="12" t="s">
+      <c r="M347" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N347" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O347" s="17"/>
-      <c r="P347" s="17"/>
-      <c r="Q347" s="17"/>
-      <c r="R347" s="17"/>
-      <c r="S347" s="17"/>
-      <c r="T347" s="17"/>
-      <c r="U347" s="17"/>
-      <c r="V347" s="17"/>
+      <c r="O347" s="16"/>
+      <c r="P347" s="16"/>
+      <c r="Q347" s="16"/>
+      <c r="R347" s="16"/>
+      <c r="S347" s="16"/>
+      <c r="T347" s="16"/>
+      <c r="U347" s="16"/>
+      <c r="V347" s="16"/>
     </row>
     <row r="348" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A348" s="25" t="s">
+      <c r="A348" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B348" s="24" t="s">
+      <c r="B348" s="23" t="s">
         <v>543</v>
       </c>
       <c r="C348" s="3" t="s">
@@ -18920,20 +18923,20 @@
       <c r="E348" s="5">
         <v>8.02</v>
       </c>
-      <c r="F348" s="12">
+      <c r="F348" s="11">
         <v>1896</v>
       </c>
-      <c r="G348" s="12">
+      <c r="G348" s="11">
         <v>1922</v>
       </c>
       <c r="H348" s="5">
         <f t="shared" si="3"/>
         <v>26.7408</v>
       </c>
-      <c r="I348" s="12" t="s">
+      <c r="I348" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J348" s="15">
+      <c r="J348" s="14">
         <f>(1+(G348-F348))*0.0096</f>
         <v>0.25919999999999999</v>
       </c>
@@ -18943,7 +18946,7 @@
       <c r="L348" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M348" s="12" t="s">
+      <c r="M348" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N348" s="6" t="s">
@@ -18951,10 +18954,10 @@
       </c>
     </row>
     <row r="349" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A349" s="25" t="s">
+      <c r="A349" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B349" s="24" t="s">
+      <c r="B349" s="23" t="s">
         <v>544</v>
       </c>
       <c r="C349" s="3" t="s">
@@ -18963,23 +18966,23 @@
       <c r="D349" s="5">
         <v>36.01</v>
       </c>
-      <c r="E349" s="15">
+      <c r="E349" s="14">
         <v>-5.6</v>
       </c>
-      <c r="F349" s="12">
+      <c r="F349" s="11">
         <v>1943</v>
       </c>
-      <c r="G349" s="12">
+      <c r="G349" s="11">
         <v>2018</v>
       </c>
       <c r="H349" s="5">
         <f t="shared" si="3"/>
         <v>71.7136</v>
       </c>
-      <c r="I349" s="12" t="s">
+      <c r="I349" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="J349" s="15">
+      <c r="J349" s="14">
         <f>(1+(G349-F349))*0.0564</f>
         <v>4.2863999999999995</v>
       </c>
@@ -18989,7 +18992,7 @@
       <c r="L349" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M349" s="12" t="s">
+      <c r="M349" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N349" s="6" t="s">
@@ -18997,10 +19000,10 @@
       </c>
     </row>
     <row r="350" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A350" s="25" t="s">
+      <c r="A350" s="24" t="s">
         <v>535</v>
       </c>
-      <c r="B350" s="24" t="s">
+      <c r="B350" s="23" t="s">
         <v>545</v>
       </c>
       <c r="C350" s="3" t="s">
@@ -19009,23 +19012,23 @@
       <c r="D350" s="5">
         <v>35.25</v>
       </c>
-      <c r="E350" s="15">
+      <c r="E350" s="14">
         <v>-3.92</v>
       </c>
-      <c r="F350" s="12">
+      <c r="F350" s="11">
         <v>1944</v>
       </c>
-      <c r="G350" s="12">
+      <c r="G350" s="11">
         <v>1949</v>
       </c>
       <c r="H350" s="5">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="I350" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J350" s="15">
+      <c r="I350" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J350" s="14">
         <v>0</v>
       </c>
       <c r="K350" s="3" t="s">
@@ -19034,7 +19037,7 @@
       <c r="L350" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M350" s="12" t="s">
+      <c r="M350" s="11" t="s">
         <v>266</v>
       </c>
       <c r="N350" s="6" t="s">
@@ -19812,7 +19815,7 @@
       <c r="A368" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B368" s="27" t="s">
+      <c r="B368" s="26" t="s">
         <v>566</v>
       </c>
       <c r="C368" s="3" t="s">
@@ -19846,7 +19849,7 @@
       <c r="L368" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M368" s="28" t="s">
+      <c r="M368" s="27" t="s">
         <v>23</v>
       </c>
       <c r="N368" s="7" t="s">
@@ -19879,7 +19882,7 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="I369" s="11" t="s">
+      <c r="I369" s="10" t="s">
         <v>740</v>
       </c>
       <c r="J369" s="5">
@@ -19894,7 +19897,7 @@
       <c r="M369" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N369" s="29" t="s">
+      <c r="N369" s="28" t="s">
         <v>572</v>
       </c>
     </row>
@@ -19924,7 +19927,7 @@
         <f t="shared" si="3"/>
         <v>91</v>
       </c>
-      <c r="I370" s="11" t="s">
+      <c r="I370" s="10" t="s">
         <v>741</v>
       </c>
       <c r="J370" s="5">
@@ -19939,7 +19942,7 @@
       <c r="M370" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="N370" s="29" t="s">
+      <c r="N370" s="28" t="s">
         <v>572</v>
       </c>
     </row>
@@ -19947,7 +19950,7 @@
       <c r="A371" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="B371" s="30" t="s">
+      <c r="B371" s="29" t="s">
         <v>574</v>
       </c>
       <c r="C371" s="3" t="s">
@@ -19993,22 +19996,22 @@
       <c r="A372" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B372" s="31" t="s">
+      <c r="B372" s="30" t="s">
         <v>578</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D372" s="32">
+      <c r="D372" s="31">
         <v>38.588610000000003</v>
       </c>
       <c r="E372" s="5">
         <v>-121.51</v>
       </c>
-      <c r="F372" s="33">
+      <c r="F372" s="32">
         <v>1919</v>
       </c>
-      <c r="G372" s="33">
+      <c r="G372" s="32">
         <f>F372+105</f>
         <v>2024</v>
       </c>
@@ -20039,22 +20042,22 @@
       <c r="A373" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B373" s="31" t="s">
+      <c r="B373" s="30" t="s">
         <v>580</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D373" s="32">
+      <c r="D373" s="31">
         <v>38.349580000000003</v>
       </c>
       <c r="E373" s="5">
         <v>-121.53355999999999</v>
       </c>
-      <c r="F373" s="33">
+      <c r="F373" s="32">
         <v>1944</v>
       </c>
-      <c r="G373" s="33">
+      <c r="G373" s="32">
         <f>F373+80</f>
         <v>2024</v>
       </c>
@@ -20085,22 +20088,22 @@
       <c r="A374" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B374" s="31" t="s">
+      <c r="B374" s="30" t="s">
         <v>581</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D374" s="32">
+      <c r="D374" s="31">
         <v>38.255279999999999</v>
       </c>
       <c r="E374" s="5">
         <v>-121.44</v>
       </c>
-      <c r="F374" s="33">
+      <c r="F374" s="32">
         <v>1959</v>
       </c>
-      <c r="G374" s="33">
+      <c r="G374" s="32">
         <f>F374+65</f>
         <v>2024</v>
       </c>
@@ -20131,7 +20134,7 @@
       <c r="A375" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B375" s="31" t="s">
+      <c r="B375" s="30" t="s">
         <v>582</v>
       </c>
       <c r="C375" s="3" t="s">
@@ -20143,10 +20146,10 @@
       <c r="E375" s="5">
         <v>-121.51674</v>
       </c>
-      <c r="F375" s="33">
+      <c r="F375" s="32">
         <v>1929</v>
       </c>
-      <c r="G375" s="33">
+      <c r="G375" s="32">
         <f>F375+95</f>
         <v>2024</v>
       </c>
@@ -20177,7 +20180,7 @@
       <c r="A376" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B376" s="31" t="s">
+      <c r="B376" s="30" t="s">
         <v>583</v>
       </c>
       <c r="C376" s="3" t="s">
@@ -20189,10 +20192,10 @@
       <c r="E376" s="5">
         <v>-121.4911</v>
       </c>
-      <c r="F376" s="33">
+      <c r="F376" s="32">
         <v>1925</v>
       </c>
-      <c r="G376" s="33">
+      <c r="G376" s="32">
         <f>F376+99</f>
         <v>2024</v>
       </c>
@@ -20223,22 +20226,22 @@
       <c r="A377" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B377" s="31" t="s">
+      <c r="B377" s="30" t="s">
         <v>584</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D377" s="32">
+      <c r="D377" s="31">
         <v>38.15972</v>
       </c>
       <c r="E377" s="5">
         <v>-121.68639</v>
       </c>
-      <c r="F377" s="33">
+      <c r="F377" s="32">
         <v>1915</v>
       </c>
-      <c r="G377" s="33">
+      <c r="G377" s="32">
         <f>F377+109</f>
         <v>2024</v>
       </c>
@@ -20269,7 +20272,7 @@
       <c r="A378" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B378" s="31" t="s">
+      <c r="B378" s="30" t="s">
         <v>585</v>
       </c>
       <c r="C378" s="3" t="s">
@@ -20281,10 +20284,10 @@
       <c r="E378" s="5">
         <v>-121.58389</v>
       </c>
-      <c r="F378" s="33">
+      <c r="F378" s="32">
         <v>1944</v>
       </c>
-      <c r="G378" s="33">
+      <c r="G378" s="32">
         <f>F378+80</f>
         <v>2024</v>
       </c>
@@ -20315,7 +20318,7 @@
       <c r="A379" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B379" s="31" t="s">
+      <c r="B379" s="30" t="s">
         <v>586</v>
       </c>
       <c r="C379" s="3" t="s">
@@ -20327,10 +20330,10 @@
       <c r="E379" s="5">
         <v>-121.69917</v>
       </c>
-      <c r="F379" s="33">
+      <c r="F379" s="32">
         <v>1944</v>
       </c>
-      <c r="G379" s="33">
+      <c r="G379" s="32">
         <f>F379+40</f>
         <v>1984</v>
       </c>
@@ -20361,7 +20364,7 @@
       <c r="A380" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B380" s="30" t="s">
+      <c r="B380" s="29" t="s">
         <v>587</v>
       </c>
       <c r="C380" s="3" t="s">
@@ -20373,10 +20376,10 @@
       <c r="E380" s="5">
         <v>-121.855</v>
       </c>
-      <c r="F380" s="33">
+      <c r="F380" s="32">
         <v>1915</v>
       </c>
-      <c r="G380" s="33">
+      <c r="G380" s="32">
         <f>F380+109</f>
         <v>2024</v>
       </c>
@@ -20407,7 +20410,7 @@
       <c r="A381" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B381" s="30" t="s">
+      <c r="B381" s="29" t="s">
         <v>588</v>
       </c>
       <c r="C381" s="3" t="s">
@@ -20419,10 +20422,10 @@
       <c r="E381" s="5">
         <v>-122.14556</v>
       </c>
-      <c r="F381" s="33">
+      <c r="F381" s="32">
         <v>1944</v>
       </c>
-      <c r="G381" s="33">
+      <c r="G381" s="32">
         <f>F381+80</f>
         <v>2024</v>
       </c>
@@ -20453,7 +20456,7 @@
       <c r="A382" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B382" s="30" t="s">
+      <c r="B382" s="29" t="s">
         <v>589</v>
       </c>
       <c r="C382" s="3" t="s">
@@ -20465,10 +20468,10 @@
       <c r="E382" s="5">
         <v>-121.80306</v>
       </c>
-      <c r="F382" s="33">
+      <c r="F382" s="32">
         <v>1934</v>
       </c>
-      <c r="G382" s="33">
+      <c r="G382" s="32">
         <f>F382+90</f>
         <v>2024</v>
       </c>
@@ -20499,7 +20502,7 @@
       <c r="A383" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B383" s="30" t="s">
+      <c r="B383" s="29" t="s">
         <v>590</v>
       </c>
       <c r="C383" s="3" t="s">
@@ -20511,10 +20514,10 @@
       <c r="E383" s="5">
         <v>-121.59139</v>
       </c>
-      <c r="F383" s="33">
+      <c r="F383" s="32">
         <v>1957</v>
       </c>
-      <c r="G383" s="33">
+      <c r="G383" s="32">
         <f>F383+64</f>
         <v>2021</v>
       </c>
@@ -20545,7 +20548,7 @@
       <c r="A384" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B384" s="30" t="s">
+      <c r="B384" s="29" t="s">
         <v>591</v>
       </c>
       <c r="C384" s="3" t="s">
@@ -20557,10 +20560,10 @@
       <c r="E384" s="5">
         <v>-121.68694000000001</v>
       </c>
-      <c r="F384" s="33">
+      <c r="F384" s="32">
         <v>1944</v>
       </c>
-      <c r="G384" s="33">
+      <c r="G384" s="32">
         <f>F384+80</f>
         <v>2024</v>
       </c>
@@ -20591,7 +20594,7 @@
       <c r="A385" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B385" s="34" t="s">
+      <c r="B385" s="33" t="s">
         <v>592</v>
       </c>
       <c r="C385" s="3" t="s">
@@ -20603,10 +20606,10 @@
       <c r="E385" s="5">
         <v>-121.49687</v>
       </c>
-      <c r="F385" s="33">
+      <c r="F385" s="32">
         <v>1928</v>
       </c>
-      <c r="G385" s="33">
+      <c r="G385" s="32">
         <f>F385+96</f>
         <v>2024</v>
       </c>
@@ -20637,7 +20640,7 @@
       <c r="A386" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B386" s="30" t="s">
+      <c r="B386" s="29" t="s">
         <v>593</v>
       </c>
       <c r="C386" s="3" t="s">
@@ -20649,10 +20652,10 @@
       <c r="E386" s="5">
         <v>-121.52381</v>
       </c>
-      <c r="F386" s="33">
+      <c r="F386" s="32">
         <v>1957</v>
       </c>
-      <c r="G386" s="33">
+      <c r="G386" s="32">
         <f>F386+67</f>
         <v>2024</v>
       </c>
@@ -20683,7 +20686,7 @@
       <c r="A387" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B387" s="30" t="s">
+      <c r="B387" s="29" t="s">
         <v>594</v>
       </c>
       <c r="C387" s="3" t="s">
@@ -20695,10 +20698,10 @@
       <c r="E387" s="5">
         <v>-121.41943999999999</v>
       </c>
-      <c r="F387" s="33">
+      <c r="F387" s="32">
         <v>1939</v>
       </c>
-      <c r="G387" s="33">
+      <c r="G387" s="32">
         <f>F387+85</f>
         <v>2024</v>
       </c>
@@ -20729,7 +20732,7 @@
       <c r="A388" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B388" s="30" t="s">
+      <c r="B388" s="29" t="s">
         <v>595</v>
       </c>
       <c r="C388" s="3" t="s">
@@ -20741,10 +20744,10 @@
       <c r="E388" s="5">
         <v>-121.58028</v>
       </c>
-      <c r="F388" s="33">
+      <c r="F388" s="32">
         <v>1945</v>
       </c>
-      <c r="G388" s="33">
+      <c r="G388" s="32">
         <f>F388+79</f>
         <v>2024</v>
       </c>
@@ -20775,7 +20778,7 @@
       <c r="A389" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B389" s="30" t="s">
+      <c r="B389" s="29" t="s">
         <v>596</v>
       </c>
       <c r="C389" s="3" t="s">
@@ -20787,10 +20790,10 @@
       <c r="E389" s="5">
         <v>-121.36556</v>
       </c>
-      <c r="F389" s="33">
+      <c r="F389" s="32">
         <v>1959</v>
       </c>
-      <c r="G389" s="33">
+      <c r="G389" s="32">
         <f>F389+65</f>
         <v>2024</v>
       </c>
@@ -20821,7 +20824,7 @@
       <c r="A390" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B390" s="30" t="s">
+      <c r="B390" s="29" t="s">
         <v>597</v>
       </c>
       <c r="C390" s="3" t="s">
@@ -20833,10 +20836,10 @@
       <c r="E390" s="5">
         <v>-121.48833</v>
       </c>
-      <c r="F390" s="33">
+      <c r="F390" s="32">
         <v>1944</v>
       </c>
-      <c r="G390" s="33">
+      <c r="G390" s="32">
         <f>F390+80</f>
         <v>2024</v>
       </c>
@@ -20867,7 +20870,7 @@
       <c r="A391" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B391" s="30" t="s">
+      <c r="B391" s="29" t="s">
         <v>598</v>
       </c>
       <c r="C391" s="3" t="s">
@@ -20879,10 +20882,10 @@
       <c r="E391" s="5">
         <v>-121.32308</v>
       </c>
-      <c r="F391" s="33">
+      <c r="F391" s="32">
         <v>1958</v>
       </c>
-      <c r="G391" s="33">
+      <c r="G391" s="32">
         <f>F391+66</f>
         <v>2024</v>
       </c>
@@ -20913,7 +20916,7 @@
       <c r="A392" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B392" s="30" t="s">
+      <c r="B392" s="29" t="s">
         <v>599</v>
       </c>
       <c r="C392" s="3" t="s">
@@ -20925,10 +20928,10 @@
       <c r="E392" s="5">
         <v>-121.38361</v>
       </c>
-      <c r="F392" s="33">
+      <c r="F392" s="32">
         <v>1958</v>
       </c>
-      <c r="G392" s="33">
+      <c r="G392" s="32">
         <f>F392+66</f>
         <v>2024</v>
       </c>
@@ -20959,7 +20962,7 @@
       <c r="A393" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B393" s="30" t="s">
+      <c r="B393" s="29" t="s">
         <v>600</v>
       </c>
       <c r="C393" s="3" t="s">
@@ -20971,10 +20974,10 @@
       <c r="E393" s="5">
         <v>-121.55301</v>
       </c>
-      <c r="F393" s="33">
+      <c r="F393" s="32">
         <v>1957</v>
       </c>
-      <c r="G393" s="33">
+      <c r="G393" s="32">
         <f>F393+67</f>
         <v>2024</v>
       </c>
@@ -21005,7 +21008,7 @@
       <c r="A394" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B394" s="30" t="s">
+      <c r="B394" s="29" t="s">
         <v>601</v>
       </c>
       <c r="C394" s="3" t="s">
@@ -21017,10 +21020,10 @@
       <c r="E394" s="5">
         <v>-121.44986</v>
       </c>
-      <c r="F394" s="33">
+      <c r="F394" s="32">
         <v>1958</v>
       </c>
-      <c r="G394" s="33">
+      <c r="G394" s="32">
         <f>F394+66</f>
         <v>2024</v>
       </c>
@@ -21051,7 +21054,7 @@
       <c r="A395" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B395" s="30" t="s">
+      <c r="B395" s="29" t="s">
         <v>602</v>
       </c>
       <c r="C395" s="3" t="s">
@@ -21063,10 +21066,10 @@
       <c r="E395" s="5">
         <v>-121.44956000000001</v>
       </c>
-      <c r="F395" s="33">
+      <c r="F395" s="32">
         <v>1957</v>
       </c>
-      <c r="G395" s="33">
+      <c r="G395" s="32">
         <f>F395+67</f>
         <v>2024</v>
       </c>
@@ -21097,7 +21100,7 @@
       <c r="A396" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B396" s="30" t="s">
+      <c r="B396" s="29" t="s">
         <v>603</v>
       </c>
       <c r="C396" s="3" t="s">
@@ -21109,10 +21112,10 @@
       <c r="E396" s="5">
         <v>-121.30649</v>
       </c>
-      <c r="F396" s="33">
+      <c r="F396" s="32">
         <v>1920</v>
       </c>
-      <c r="G396" s="33">
+      <c r="G396" s="32">
         <f>F396+104</f>
         <v>2024</v>
       </c>
@@ -21143,31 +21146,31 @@
       <c r="A397" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B397" s="35" t="s">
+      <c r="B397" s="34" t="s">
         <v>604</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D397" s="36">
+      <c r="D397" s="35">
         <v>38.608049999999999</v>
       </c>
-      <c r="E397" s="36">
+      <c r="E397" s="35">
         <v>-121.55929999999999</v>
       </c>
-      <c r="F397" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G397" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H397" s="36">
+      <c r="F397" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G397" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H397" s="35">
         <v>54</v>
       </c>
-      <c r="I397" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J397" s="33" t="s">
+      <c r="I397" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J397" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K397" s="3" t="s">
@@ -21187,31 +21190,31 @@
       <c r="A398" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B398" s="35" t="s">
+      <c r="B398" s="34" t="s">
         <v>605</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D398" s="36">
+      <c r="D398" s="35">
         <v>38.600099999999998</v>
       </c>
-      <c r="E398" s="36">
+      <c r="E398" s="35">
         <v>-121.53954</v>
       </c>
-      <c r="F398" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G398" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H398" s="36">
+      <c r="F398" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G398" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H398" s="35">
         <v>9</v>
       </c>
-      <c r="I398" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J398" s="33" t="s">
+      <c r="I398" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J398" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K398" s="3" t="s">
@@ -21231,31 +21234,31 @@
       <c r="A399" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B399" s="35" t="s">
+      <c r="B399" s="34" t="s">
         <v>606</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D399" s="36">
+      <c r="D399" s="35">
         <v>38.474780000000003</v>
       </c>
-      <c r="E399" s="36">
+      <c r="E399" s="35">
         <v>-121.58823</v>
       </c>
-      <c r="F399" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G399" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H399" s="36">
+      <c r="F399" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G399" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H399" s="35">
         <v>65</v>
       </c>
-      <c r="I399" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J399" s="33" t="s">
+      <c r="I399" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J399" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K399" s="3" t="s">
@@ -21275,31 +21278,31 @@
       <c r="A400" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B400" s="35" t="s">
+      <c r="B400" s="34" t="s">
         <v>607</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D400" s="36">
+      <c r="D400" s="35">
         <v>38.456110000000002</v>
       </c>
-      <c r="E400" s="36">
+      <c r="E400" s="35">
         <v>-121.5003</v>
       </c>
-      <c r="F400" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G400" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H400" s="36">
+      <c r="F400" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G400" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H400" s="35">
         <v>30</v>
       </c>
-      <c r="I400" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J400" s="33" t="s">
+      <c r="I400" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J400" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K400" s="3" t="s">
@@ -21319,31 +21322,31 @@
       <c r="A401" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B401" s="35" t="s">
+      <c r="B401" s="34" t="s">
         <v>608</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D401" s="36">
+      <c r="D401" s="35">
         <v>38.417839999999998</v>
       </c>
-      <c r="E401" s="36">
+      <c r="E401" s="35">
         <v>-121.52506</v>
       </c>
-      <c r="F401" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G401" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H401" s="36">
+      <c r="F401" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G401" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H401" s="35">
         <v>29</v>
       </c>
-      <c r="I401" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J401" s="33" t="s">
+      <c r="I401" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J401" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K401" s="3" t="s">
@@ -21363,31 +21366,31 @@
       <c r="A402" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B402" s="35" t="s">
+      <c r="B402" s="34" t="s">
         <v>609</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D402" s="36">
+      <c r="D402" s="35">
         <v>38.36797</v>
       </c>
-      <c r="E402" s="36">
+      <c r="E402" s="35">
         <v>-121.52134</v>
       </c>
-      <c r="F402" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G402" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H402" s="36">
+      <c r="F402" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G402" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H402" s="35">
         <v>12</v>
       </c>
-      <c r="I402" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J402" s="33" t="s">
+      <c r="I402" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J402" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K402" s="3" t="s">
@@ -21407,31 +21410,31 @@
       <c r="A403" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B403" s="35" t="s">
+      <c r="B403" s="34" t="s">
         <v>610</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D403" s="36">
+      <c r="D403" s="35">
         <v>38.329279999999997</v>
       </c>
-      <c r="E403" s="36">
+      <c r="E403" s="35">
         <v>-121.69398</v>
       </c>
-      <c r="F403" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G403" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H403" s="36">
+      <c r="F403" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G403" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H403" s="35">
         <v>36</v>
       </c>
-      <c r="I403" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J403" s="33" t="s">
+      <c r="I403" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J403" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K403" s="3" t="s">
@@ -21451,31 +21454,31 @@
       <c r="A404" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B404" s="35" t="s">
+      <c r="B404" s="34" t="s">
         <v>611</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D404" s="36">
+      <c r="D404" s="35">
         <v>38.290120000000002</v>
       </c>
-      <c r="E404" s="36">
+      <c r="E404" s="35">
         <v>-121.64478</v>
       </c>
-      <c r="F404" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G404" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H404" s="36">
+      <c r="F404" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G404" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H404" s="35">
         <v>13</v>
       </c>
-      <c r="I404" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J404" s="33" t="s">
+      <c r="I404" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J404" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K404" s="3" t="s">
@@ -21495,31 +21498,31 @@
       <c r="A405" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B405" s="35" t="s">
+      <c r="B405" s="34" t="s">
         <v>612</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D405" s="36">
+      <c r="D405" s="35">
         <v>38.284999999999997</v>
       </c>
-      <c r="E405" s="36">
+      <c r="E405" s="35">
         <v>-121.587</v>
       </c>
-      <c r="F405" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G405" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H405" s="36">
+      <c r="F405" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G405" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H405" s="35">
         <v>2</v>
       </c>
-      <c r="I405" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J405" s="33" t="s">
+      <c r="I405" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J405" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K405" s="3" t="s">
@@ -21539,31 +21542,31 @@
       <c r="A406" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B406" s="35" t="s">
+      <c r="B406" s="34" t="s">
         <v>613</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D406" s="36">
+      <c r="D406" s="35">
         <v>38.244720000000001</v>
       </c>
-      <c r="E406" s="36">
+      <c r="E406" s="35">
         <v>-121.50528</v>
       </c>
-      <c r="F406" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G406" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H406" s="36">
-        <v>10</v>
-      </c>
-      <c r="I406" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J406" s="33" t="s">
+      <c r="F406" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G406" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H406" s="35">
+        <v>10</v>
+      </c>
+      <c r="I406" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J406" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K406" s="3" t="s">
@@ -21583,31 +21586,31 @@
       <c r="A407" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B407" s="35" t="s">
+      <c r="B407" s="34" t="s">
         <v>614</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D407" s="36">
+      <c r="D407" s="35">
         <v>38.228299999999997</v>
       </c>
-      <c r="E407" s="36">
+      <c r="E407" s="35">
         <v>-121.6722</v>
       </c>
-      <c r="F407" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G407" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H407" s="36">
+      <c r="F407" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G407" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H407" s="35">
         <v>4</v>
       </c>
-      <c r="I407" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J407" s="33" t="s">
+      <c r="I407" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J407" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K407" s="3" t="s">
@@ -21627,31 +21630,31 @@
       <c r="A408" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B408" s="35" t="s">
+      <c r="B408" s="34" t="s">
         <v>615</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D408" s="36">
+      <c r="D408" s="35">
         <v>38.186259999999997</v>
       </c>
-      <c r="E408" s="36">
+      <c r="E408" s="35">
         <v>-121.971</v>
       </c>
-      <c r="F408" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G408" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H408" s="36">
+      <c r="F408" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G408" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H408" s="35">
         <v>1</v>
       </c>
-      <c r="I408" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J408" s="33" t="s">
+      <c r="I408" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J408" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K408" s="3" t="s">
@@ -21671,31 +21674,31 @@
       <c r="A409" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B409" s="35" t="s">
+      <c r="B409" s="34" t="s">
         <v>616</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D409" s="36">
+      <c r="D409" s="35">
         <v>38.167140000000003</v>
       </c>
-      <c r="E409" s="36">
+      <c r="E409" s="35">
         <v>-121.93389000000001</v>
       </c>
-      <c r="F409" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G409" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H409" s="36">
+      <c r="F409" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G409" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H409" s="35">
         <v>1</v>
       </c>
-      <c r="I409" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J409" s="33" t="s">
+      <c r="I409" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J409" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K409" s="3" t="s">
@@ -21715,31 +21718,31 @@
       <c r="A410" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B410" s="35" t="s">
+      <c r="B410" s="34" t="s">
         <v>617</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D410" s="36">
+      <c r="D410" s="35">
         <v>38.163330000000002</v>
       </c>
-      <c r="E410" s="36">
+      <c r="E410" s="35">
         <v>-121.60833</v>
       </c>
-      <c r="F410" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G410" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H410" s="36">
+      <c r="F410" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G410" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H410" s="35">
         <v>19</v>
       </c>
-      <c r="I410" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J410" s="33" t="s">
+      <c r="I410" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J410" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K410" s="3" t="s">
@@ -21759,31 +21762,31 @@
       <c r="A411" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B411" s="35" t="s">
+      <c r="B411" s="34" t="s">
         <v>618</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D411" s="36">
+      <c r="D411" s="35">
         <v>38.110869999999998</v>
       </c>
-      <c r="E411" s="36">
+      <c r="E411" s="35">
         <v>-121.9718</v>
       </c>
-      <c r="F411" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G411" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H411" s="36">
+      <c r="F411" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G411" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H411" s="35">
         <v>5</v>
       </c>
-      <c r="I411" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J411" s="33" t="s">
+      <c r="I411" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J411" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K411" s="3" t="s">
@@ -21803,31 +21806,31 @@
       <c r="A412" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B412" s="35" t="s">
+      <c r="B412" s="34" t="s">
         <v>619</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D412" s="36">
+      <c r="D412" s="35">
         <v>38.108530000000002</v>
       </c>
-      <c r="E412" s="36">
+      <c r="E412" s="35">
         <v>-122.05598000000001</v>
       </c>
-      <c r="F412" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G412" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H412" s="36">
+      <c r="F412" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G412" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H412" s="35">
         <v>4</v>
       </c>
-      <c r="I412" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J412" s="33" t="s">
+      <c r="I412" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J412" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K412" s="3" t="s">
@@ -21847,31 +21850,31 @@
       <c r="A413" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B413" s="35" t="s">
+      <c r="B413" s="34" t="s">
         <v>620</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D413" s="36">
+      <c r="D413" s="35">
         <v>38.09639</v>
       </c>
-      <c r="E413" s="36">
+      <c r="E413" s="35">
         <v>-121.49611</v>
       </c>
-      <c r="F413" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G413" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H413" s="36">
+      <c r="F413" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G413" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H413" s="35">
         <v>13</v>
       </c>
-      <c r="I413" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J413" s="33" t="s">
+      <c r="I413" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J413" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K413" s="3" t="s">
@@ -21891,31 +21894,31 @@
       <c r="A414" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B414" s="35" t="s">
+      <c r="B414" s="34" t="s">
         <v>621</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D414" s="36">
+      <c r="D414" s="35">
         <v>38.07</v>
       </c>
-      <c r="E414" s="36">
+      <c r="E414" s="35">
         <v>-122.25</v>
       </c>
-      <c r="F414" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G414" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H414" s="36">
+      <c r="F414" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G414" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H414" s="35">
         <v>20</v>
       </c>
-      <c r="I414" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J414" s="33" t="s">
+      <c r="I414" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J414" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K414" s="3" t="s">
@@ -21935,31 +21938,31 @@
       <c r="A415" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B415" s="35" t="s">
+      <c r="B415" s="34" t="s">
         <v>622</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D415" s="36">
+      <c r="D415" s="35">
         <v>38.056789999999999</v>
       </c>
-      <c r="E415" s="36">
+      <c r="E415" s="35">
         <v>-121.99997</v>
       </c>
-      <c r="F415" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G415" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H415" s="36">
+      <c r="F415" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G415" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H415" s="35">
         <v>1</v>
       </c>
-      <c r="I415" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J415" s="33" t="s">
+      <c r="I415" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J415" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K415" s="3" t="s">
@@ -21979,31 +21982,31 @@
       <c r="A416" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B416" s="35" t="s">
+      <c r="B416" s="34" t="s">
         <v>623</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D416" s="36">
+      <c r="D416" s="35">
         <v>38.055799999999998</v>
       </c>
-      <c r="E416" s="36">
+      <c r="E416" s="35">
         <v>-121.6669</v>
       </c>
-      <c r="F416" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G416" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H416" s="36">
+      <c r="F416" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G416" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H416" s="35">
         <v>2</v>
       </c>
-      <c r="I416" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J416" s="33" t="s">
+      <c r="I416" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J416" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K416" s="3" t="s">
@@ -22023,31 +22026,31 @@
       <c r="A417" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B417" s="35" t="s">
+      <c r="B417" s="34" t="s">
         <v>624</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D417" s="36">
+      <c r="D417" s="35">
         <v>38.042969999999997</v>
       </c>
-      <c r="E417" s="36">
+      <c r="E417" s="35">
         <v>-121.89248000000001</v>
       </c>
-      <c r="F417" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G417" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H417" s="36">
+      <c r="F417" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G417" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H417" s="35">
         <v>2</v>
       </c>
-      <c r="I417" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J417" s="33" t="s">
+      <c r="I417" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J417" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K417" s="3" t="s">
@@ -22067,31 +22070,31 @@
       <c r="A418" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B418" s="35" t="s">
+      <c r="B418" s="34" t="s">
         <v>625</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D418" s="36">
+      <c r="D418" s="35">
         <v>38.042700000000004</v>
       </c>
-      <c r="E418" s="36">
+      <c r="E418" s="35">
         <v>-121.92024000000001</v>
       </c>
-      <c r="F418" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G418" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H418" s="36">
-        <v>16</v>
-      </c>
-      <c r="I418" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J418" s="33" t="s">
+      <c r="F418" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G418" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H418" s="35">
+        <v>16</v>
+      </c>
+      <c r="I418" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J418" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K418" s="3" t="s">
@@ -22111,31 +22114,31 @@
       <c r="A419" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B419" s="35" t="s">
+      <c r="B419" s="34" t="s">
         <v>626</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D419" s="36">
+      <c r="D419" s="35">
         <v>38.041089999999997</v>
       </c>
-      <c r="E419" s="36">
+      <c r="E419" s="35">
         <v>-121.63218999999999</v>
       </c>
-      <c r="F419" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G419" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H419" s="36">
+      <c r="F419" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G419" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H419" s="35">
         <v>2</v>
       </c>
-      <c r="I419" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J419" s="33" t="s">
+      <c r="I419" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J419" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K419" s="3" t="s">
@@ -22155,31 +22158,31 @@
       <c r="A420" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B420" s="35" t="s">
+      <c r="B420" s="34" t="s">
         <v>627</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D420" s="36">
+      <c r="D420" s="35">
         <v>38.006990000000002</v>
       </c>
-      <c r="E420" s="36">
+      <c r="E420" s="35">
         <v>-121.58062</v>
       </c>
-      <c r="F420" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G420" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H420" s="36">
+      <c r="F420" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G420" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H420" s="35">
         <v>9</v>
       </c>
-      <c r="I420" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J420" s="33" t="s">
+      <c r="I420" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J420" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K420" s="3" t="s">
@@ -22199,31 +22202,31 @@
       <c r="A421" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B421" s="35" t="s">
+      <c r="B421" s="34" t="s">
         <v>628</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D421" s="36">
+      <c r="D421" s="35">
         <v>37.976309999999998</v>
       </c>
-      <c r="E421" s="36">
+      <c r="E421" s="35">
         <v>-121.63760000000001</v>
       </c>
-      <c r="F421" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G421" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H421" s="36">
-        <v>16</v>
-      </c>
-      <c r="I421" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J421" s="33" t="s">
+      <c r="F421" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G421" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H421" s="35">
+        <v>16</v>
+      </c>
+      <c r="I421" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J421" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K421" s="3" t="s">
@@ -22243,31 +22246,31 @@
       <c r="A422" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B422" s="35" t="s">
+      <c r="B422" s="34" t="s">
         <v>629</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D422" s="36">
+      <c r="D422" s="35">
         <v>37.953749999999999</v>
       </c>
-      <c r="E422" s="36">
+      <c r="E422" s="35">
         <v>-121.29557</v>
       </c>
-      <c r="F422" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G422" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H422" s="36">
+      <c r="F422" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G422" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H422" s="35">
         <v>38</v>
       </c>
-      <c r="I422" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J422" s="33" t="s">
+      <c r="I422" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J422" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K422" s="3" t="s">
@@ -22287,31 +22290,31 @@
       <c r="A423" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B423" s="35" t="s">
+      <c r="B423" s="34" t="s">
         <v>630</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D423" s="36">
+      <c r="D423" s="35">
         <v>37.91028</v>
       </c>
-      <c r="E423" s="36">
+      <c r="E423" s="35">
         <v>-121.56083</v>
       </c>
-      <c r="F423" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G423" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H423" s="36">
+      <c r="F423" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G423" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H423" s="35">
         <v>26</v>
       </c>
-      <c r="I423" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J423" s="33" t="s">
+      <c r="I423" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J423" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K423" s="3" t="s">
@@ -22331,31 +22334,31 @@
       <c r="A424" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B424" s="35" t="s">
+      <c r="B424" s="34" t="s">
         <v>631</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D424" s="36">
+      <c r="D424" s="35">
         <v>37.891039999999997</v>
       </c>
-      <c r="E424" s="36">
+      <c r="E424" s="35">
         <v>-121.57023</v>
       </c>
-      <c r="F424" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G424" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="H424" s="36">
+      <c r="F424" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G424" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H424" s="35">
         <v>20</v>
       </c>
-      <c r="I424" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J424" s="33" t="s">
+      <c r="I424" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J424" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K424" s="3" t="s">
@@ -22375,31 +22378,31 @@
       <c r="A425" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B425" s="35" t="s">
+      <c r="B425" s="34" t="s">
         <v>632</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D425" s="36">
+      <c r="D425" s="35">
         <v>37.859929999999999</v>
       </c>
-      <c r="E425" s="36">
+      <c r="E425" s="35">
         <v>-121.58105999999999</v>
       </c>
-      <c r="F425" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G425" s="33" t="s">
+      <c r="F425" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G425" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H425" s="5">
         <v>19</v>
       </c>
-      <c r="I425" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J425" s="33" t="s">
+      <c r="I425" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J425" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K425" s="3" t="s">
@@ -22419,31 +22422,31 @@
       <c r="A426" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B426" s="35" t="s">
+      <c r="B426" s="34" t="s">
         <v>633</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D426" s="36">
+      <c r="D426" s="35">
         <v>37.807609999999997</v>
       </c>
-      <c r="E426" s="36">
+      <c r="E426" s="35">
         <v>-121.28128</v>
       </c>
-      <c r="F426" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G426" s="33" t="s">
+      <c r="F426" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G426" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H426" s="5">
         <v>11</v>
       </c>
-      <c r="I426" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J426" s="33" t="s">
+      <c r="I426" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J426" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K426" s="3" t="s">
@@ -22463,31 +22466,31 @@
       <c r="A427" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B427" s="35" t="s">
+      <c r="B427" s="34" t="s">
         <v>634</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D427" s="36">
+      <c r="D427" s="35">
         <v>37.790529999999997</v>
       </c>
-      <c r="E427" s="36">
+      <c r="E427" s="35">
         <v>-121.41862999999999</v>
       </c>
-      <c r="F427" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G427" s="33" t="s">
+      <c r="F427" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G427" s="32" t="s">
         <v>16</v>
       </c>
       <c r="H427" s="5">
         <v>31</v>
       </c>
-      <c r="I427" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J427" s="33" t="s">
+      <c r="I427" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J427" s="32" t="s">
         <v>16</v>
       </c>
       <c r="K427" s="3" t="s">
@@ -22679,7 +22682,7 @@
       <c r="M431" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N431" s="46" t="s">
+      <c r="N431" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22724,7 +22727,7 @@
       <c r="M432" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="N432" s="46" t="s">
+      <c r="N432" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22769,7 +22772,7 @@
       <c r="M433" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N433" s="46" t="s">
+      <c r="N433" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22814,7 +22817,7 @@
       <c r="M434" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="N434" s="46" t="s">
+      <c r="N434" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22859,7 +22862,7 @@
       <c r="M435" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N435" s="46" t="s">
+      <c r="N435" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22904,7 +22907,7 @@
       <c r="M436" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N436" s="46" t="s">
+      <c r="N436" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22949,7 +22952,7 @@
       <c r="M437" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N437" s="46" t="s">
+      <c r="N437" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -22994,7 +22997,7 @@
       <c r="M438" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N438" s="46" t="s">
+      <c r="N438" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23039,7 +23042,7 @@
       <c r="M439" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N439" s="46" t="s">
+      <c r="N439" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23084,7 +23087,7 @@
       <c r="M440" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N440" s="46" t="s">
+      <c r="N440" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23129,7 +23132,7 @@
       <c r="M441" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N441" s="46" t="s">
+      <c r="N441" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23174,7 +23177,7 @@
       <c r="M442" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N442" s="46" t="s">
+      <c r="N442" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23219,7 +23222,7 @@
       <c r="M443" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N443" s="46" t="s">
+      <c r="N443" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23264,7 +23267,7 @@
       <c r="M444" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N444" s="46" t="s">
+      <c r="N444" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23309,7 +23312,7 @@
       <c r="M445" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N445" s="46" t="s">
+      <c r="N445" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23354,7 +23357,7 @@
       <c r="M446" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N446" s="46" t="s">
+      <c r="N446" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23399,7 +23402,7 @@
       <c r="M447" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N447" s="46" t="s">
+      <c r="N447" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23444,7 +23447,7 @@
       <c r="M448" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N448" s="46" t="s">
+      <c r="N448" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23489,7 +23492,7 @@
       <c r="M449" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N449" s="46" t="s">
+      <c r="N449" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23534,7 +23537,7 @@
       <c r="M450" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N450" s="46" t="s">
+      <c r="N450" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23579,7 +23582,7 @@
       <c r="M451" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N451" s="46" t="s">
+      <c r="N451" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23624,7 +23627,7 @@
       <c r="M452" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N452" s="46" t="s">
+      <c r="N452" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23669,7 +23672,7 @@
       <c r="M453" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="N453" s="46" t="s">
+      <c r="N453" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23708,13 +23711,13 @@
       <c r="K454" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="L454" s="12" t="s">
+      <c r="L454" s="11" t="s">
         <v>10</v>
       </c>
       <c r="M454" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="N454" s="46" t="s">
+      <c r="N454" s="45" t="s">
         <v>682</v>
       </c>
     </row>
@@ -23750,56 +23753,56 @@
       <c r="K455" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="L455" s="12" t="s">
+      <c r="L455" s="11" t="s">
         <v>10</v>
       </c>
       <c r="M455" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="N455" s="46" t="s">
+      <c r="N455" s="45" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="456" spans="1:23" s="37" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A456" s="38"/>
-      <c r="B456" s="37" t="s">
+    <row r="456" spans="1:23" s="36" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A456" s="37"/>
+      <c r="B456" s="36" t="s">
         <v>672</v>
       </c>
-      <c r="C456" s="37" t="s">
+      <c r="C456" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D456" s="39">
+      <c r="D456" s="38">
         <v>55.893051999999997</v>
       </c>
-      <c r="E456" s="39">
+      <c r="E456" s="38">
         <v>-4.4018449999999998</v>
       </c>
-      <c r="F456" s="37">
+      <c r="F456" s="36">
         <v>1908</v>
       </c>
-      <c r="G456" s="37">
+      <c r="G456" s="36">
         <v>1970</v>
       </c>
-      <c r="H456" s="39">
+      <c r="H456" s="38">
         <f>(1+(G456-F456))-J456</f>
         <v>1.2115384615384599</v>
       </c>
-      <c r="I456" s="37" t="s">
+      <c r="I456" s="36" t="s">
         <v>670</v>
       </c>
-      <c r="J456" s="39">
+      <c r="J456" s="38">
         <v>61.78846153846154</v>
       </c>
-      <c r="K456" s="37" t="s">
+      <c r="K456" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="L456" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="M456" s="37" t="s">
+      <c r="L456" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="M456" s="36" t="s">
         <v>524</v>
       </c>
-      <c r="N456" s="46" t="s">
+      <c r="N456" s="45" t="s">
         <v>682</v>
       </c>
       <c r="O456"/>
@@ -23849,135 +23852,135 @@
       <c r="M457" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="N457" s="46" t="s">
+      <c r="N457" s="45" t="s">
         <v>682</v>
       </c>
-      <c r="W457" s="45"/>
+      <c r="W457" s="44"/>
     </row>
     <row r="458" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A458" s="40"/>
-      <c r="D458" s="41"/>
-      <c r="E458" s="41"/>
-      <c r="H458" s="41"/>
-      <c r="J458" s="41"/>
+      <c r="A458" s="39"/>
+      <c r="D458" s="40"/>
+      <c r="E458" s="40"/>
+      <c r="H458" s="40"/>
+      <c r="J458" s="40"/>
     </row>
     <row r="459" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A459" s="40"/>
-      <c r="D459" s="41"/>
-      <c r="E459" s="41"/>
-      <c r="H459" s="41"/>
-      <c r="J459" s="41"/>
+      <c r="A459" s="39"/>
+      <c r="D459" s="40"/>
+      <c r="E459" s="40"/>
+      <c r="H459" s="40"/>
+      <c r="J459" s="40"/>
     </row>
     <row r="460" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A460" s="40"/>
-      <c r="D460" s="41"/>
-      <c r="E460" s="41"/>
-      <c r="H460" s="41"/>
-      <c r="J460" s="41"/>
+      <c r="A460" s="39"/>
+      <c r="D460" s="40"/>
+      <c r="E460" s="40"/>
+      <c r="H460" s="40"/>
+      <c r="J460" s="40"/>
     </row>
     <row r="461" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A461" s="40"/>
-      <c r="D461" s="41"/>
-      <c r="E461" s="41"/>
-      <c r="H461" s="41"/>
-      <c r="J461" s="41"/>
+      <c r="A461" s="39"/>
+      <c r="D461" s="40"/>
+      <c r="E461" s="40"/>
+      <c r="H461" s="40"/>
+      <c r="J461" s="40"/>
     </row>
     <row r="462" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A462" s="40"/>
-      <c r="D462" s="41"/>
-      <c r="E462" s="41"/>
-      <c r="H462" s="41"/>
-      <c r="J462" s="41"/>
+      <c r="A462" s="39"/>
+      <c r="D462" s="40"/>
+      <c r="E462" s="40"/>
+      <c r="H462" s="40"/>
+      <c r="J462" s="40"/>
     </row>
     <row r="463" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A463" s="40"/>
-      <c r="D463" s="41"/>
-      <c r="E463" s="41"/>
-      <c r="H463" s="41"/>
-      <c r="J463" s="41"/>
+      <c r="A463" s="39"/>
+      <c r="D463" s="40"/>
+      <c r="E463" s="40"/>
+      <c r="H463" s="40"/>
+      <c r="J463" s="40"/>
     </row>
     <row r="464" spans="1:23" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D464" s="41"/>
-      <c r="E464" s="41"/>
-      <c r="H464" s="41"/>
-      <c r="J464" s="41"/>
+      <c r="D464" s="40"/>
+      <c r="E464" s="40"/>
+      <c r="H464" s="40"/>
+      <c r="J464" s="40"/>
     </row>
     <row r="465" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A465" s="40"/>
-      <c r="D465" s="41"/>
-      <c r="E465" s="41"/>
-      <c r="H465" s="41"/>
-      <c r="J465" s="41"/>
+      <c r="A465" s="39"/>
+      <c r="D465" s="40"/>
+      <c r="E465" s="40"/>
+      <c r="H465" s="40"/>
+      <c r="J465" s="40"/>
     </row>
     <row r="466" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A466" s="40"/>
-      <c r="D466" s="41"/>
-      <c r="E466" s="41"/>
-      <c r="H466" s="41"/>
-      <c r="J466" s="41"/>
+      <c r="A466" s="39"/>
+      <c r="D466" s="40"/>
+      <c r="E466" s="40"/>
+      <c r="H466" s="40"/>
+      <c r="J466" s="40"/>
     </row>
     <row r="467" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A467" s="40"/>
-      <c r="D467" s="41"/>
-      <c r="E467" s="41"/>
-      <c r="H467" s="41"/>
-      <c r="J467" s="41"/>
+      <c r="A467" s="39"/>
+      <c r="D467" s="40"/>
+      <c r="E467" s="40"/>
+      <c r="H467" s="40"/>
+      <c r="J467" s="40"/>
     </row>
     <row r="468" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A468" s="40"/>
-      <c r="D468" s="41"/>
-      <c r="E468" s="41"/>
-      <c r="H468" s="41"/>
-      <c r="J468" s="41"/>
+      <c r="A468" s="39"/>
+      <c r="D468" s="40"/>
+      <c r="E468" s="40"/>
+      <c r="H468" s="40"/>
+      <c r="J468" s="40"/>
     </row>
     <row r="469" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A469" s="40"/>
-      <c r="D469" s="41"/>
-      <c r="E469" s="41"/>
-      <c r="H469" s="41"/>
-      <c r="J469" s="41"/>
+      <c r="A469" s="39"/>
+      <c r="D469" s="40"/>
+      <c r="E469" s="40"/>
+      <c r="H469" s="40"/>
+      <c r="J469" s="40"/>
     </row>
     <row r="470" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A470" s="40"/>
-      <c r="D470" s="41"/>
-      <c r="E470" s="41"/>
-      <c r="H470" s="41"/>
-      <c r="J470" s="41"/>
+      <c r="A470" s="39"/>
+      <c r="D470" s="40"/>
+      <c r="E470" s="40"/>
+      <c r="H470" s="40"/>
+      <c r="J470" s="40"/>
     </row>
     <row r="471" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A471" s="40"/>
-      <c r="D471" s="41"/>
-      <c r="E471" s="41"/>
-      <c r="H471" s="41"/>
-      <c r="J471" s="41"/>
+      <c r="A471" s="39"/>
+      <c r="D471" s="40"/>
+      <c r="E471" s="40"/>
+      <c r="H471" s="40"/>
+      <c r="J471" s="40"/>
     </row>
     <row r="472" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A472" s="40"/>
-      <c r="D472" s="41"/>
-      <c r="E472" s="41"/>
-      <c r="H472" s="41"/>
-      <c r="J472" s="41"/>
+      <c r="A472" s="39"/>
+      <c r="D472" s="40"/>
+      <c r="E472" s="40"/>
+      <c r="H472" s="40"/>
+      <c r="J472" s="40"/>
     </row>
     <row r="473" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A473" s="40"/>
-      <c r="D473" s="41"/>
-      <c r="E473" s="41"/>
-      <c r="H473" s="41"/>
-      <c r="J473" s="41"/>
+      <c r="A473" s="39"/>
+      <c r="D473" s="40"/>
+      <c r="E473" s="40"/>
+      <c r="H473" s="40"/>
+      <c r="J473" s="40"/>
     </row>
     <row r="474" spans="1:22" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A474" s="40"/>
-      <c r="D474" s="41"/>
-      <c r="E474" s="41"/>
-      <c r="H474" s="41"/>
-      <c r="J474" s="41"/>
-    </row>
-    <row r="475" spans="1:22" s="43" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A475" s="42"/>
-      <c r="D475" s="44"/>
-      <c r="E475" s="44"/>
-      <c r="H475" s="44"/>
-      <c r="J475" s="44"/>
+      <c r="A474" s="39"/>
+      <c r="D474" s="40"/>
+      <c r="E474" s="40"/>
+      <c r="H474" s="40"/>
+      <c r="J474" s="40"/>
+    </row>
+    <row r="475" spans="1:22" s="42" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A475" s="41"/>
+      <c r="D475" s="43"/>
+      <c r="E475" s="43"/>
+      <c r="H475" s="43"/>
+      <c r="J475" s="43"/>
       <c r="O475"/>
       <c r="P475"/>
       <c r="Q475"/>
@@ -24137,5 +24140,6 @@
     <hyperlink ref="N373:N427" r:id="rId145" display="https://rmets.onlinelibrary.wiley.com/doi/10.1002/gdj3.70018" xr:uid="{2AE06458-373C-4EA5-A2D0-341741B707F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId146"/>
 </worksheet>
 </file>